--- a/ESWE_Versorgungs_AG_Financial_Model_2021_2025.xlsx
+++ b/ESWE_Versorgungs_AG_Financial_Model_2021_2025.xlsx
@@ -31,7 +31,7 @@
     <numFmt numFmtId="166" formatCode="0.0\x;[Red]\(0.0\x\);\-"/>
     <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\);\-"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -114,6 +114,27 @@
     <font>
       <name val="Univers for Metzler"/>
       <b val="1"/>
+      <color rgb="FF003D7C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Univers for Metzler"/>
+      <b val="1"/>
+      <color rgb="FF003D7C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Univers for Metzler"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Univers for Metzler"/>
+      <color rgb="FF008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Univers for Metzler"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="14"/>
     </font>
@@ -129,7 +150,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -146,8 +167,13 @@
         <fgColor rgb="003157E3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A5CAFB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -173,11 +199,89 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF003D7C"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF003D7C"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF003D7C"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF003D7C"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF003D7C"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF003D7C"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF003D7C"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF003D7C"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF003D7C"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF003D7C"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF003D7C"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF003D7C"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -215,16 +319,46 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -239,7 +373,19 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -254,7 +400,13 @@
     <xf numFmtId="165" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -266,7 +418,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -290,10 +442,10 @@
     <xf numFmtId="167" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -902,13 +1054,13 @@
   </cols>
   <sheetData>
     <row r="2" ht="21" customHeight="1">
-      <c r="B2" s="28" t="inlineStr">
+      <c r="B2" s="44" t="inlineStr">
         <is>
           <t>ESWE Versorgungs AG – Quellen und Hinweise</t>
         </is>
       </c>
-      <c r="C2" s="28" t="n"/>
-      <c r="D2" s="28" t="n"/>
+      <c r="C2" s="44" t="n"/>
+      <c r="D2" s="44" t="n"/>
     </row>
     <row r="3">
       <c r="B3" s="5" t="inlineStr">
@@ -923,200 +1075,200 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="61" t="inlineStr">
         <is>
           <t>Gesellschaft</t>
         </is>
       </c>
-      <c r="C4" s="46" t="inlineStr">
+      <c r="C4" s="62" t="inlineStr">
         <is>
           <t>ESWE Versorgungs AG, Konradinerallee 25, 65189 Wiesbaden – Amtsgericht Wiesbaden, HRB 2105.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="45" t="inlineStr">
+      <c r="B5" s="61" t="inlineStr">
         <is>
           <t>Berichtsumfang</t>
         </is>
       </c>
-      <c r="C5" s="46" t="inlineStr">
+      <c r="C5" s="62" t="inlineStr">
         <is>
           <t>Dargestellt ist ausschließlich der HGB-Einzelabschluss der Geschäftsjahre 2021 bis 2025. Die Tätigkeitsabschlüsse nach § 6b EnWG sind nicht Bestandteil dieser Auswertung.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="45" t="inlineStr"/>
-      <c r="C6" s="46" t="inlineStr">
+      <c r="B6" s="61" t="inlineStr"/>
+      <c r="C6" s="62" t="inlineStr">
         <is>
           <t>Ein Konzernabschluss wird nicht aufgestellt (§ 291 Abs. 1 HGB – Einbeziehung in den Konzernabschluss der WVV Wiesbaden Holding GmbH).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="45" t="inlineStr">
+      <c r="B7" s="61" t="inlineStr">
         <is>
           <t>Quelle GJ 2021</t>
         </is>
       </c>
-      <c r="C7" s="46" t="inlineStr">
+      <c r="C7" s="62" t="inlineStr">
         <is>
           <t>Jahres- und Tätigkeitsabschluss nach EnWG zum 31.12.2021, Auszug aus dem Unternehmensregister.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="B8" s="45" t="inlineStr">
+      <c r="B8" s="61" t="inlineStr">
         <is>
           <t>Quelle GJ 2022</t>
         </is>
       </c>
-      <c r="C8" s="46" t="inlineStr">
+      <c r="C8" s="62" t="inlineStr">
         <is>
           <t>Jahres- und Tätigkeitsabschluss nach EnWG zum 31.12.2022, Auszug aus dem Unternehmensregister.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="B9" s="45" t="inlineStr">
+      <c r="B9" s="61" t="inlineStr">
         <is>
           <t>Quelle GJ 2023</t>
         </is>
       </c>
-      <c r="C9" s="46" t="inlineStr">
+      <c r="C9" s="62" t="inlineStr">
         <is>
           <t>Jahresabschluss zum 31.12.2023 und Tätigkeitsabschluss, Auszug aus dem Unternehmensregister.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="45" t="inlineStr">
+      <c r="B10" s="61" t="inlineStr">
         <is>
           <t>Quelle GJ 2024</t>
         </is>
       </c>
-      <c r="C10" s="46" t="inlineStr">
+      <c r="C10" s="62" t="inlineStr">
         <is>
           <t>Jahres- und Tätigkeitsabschluss nach EnWG zum 31.12.2024, Tag der Erstellung 16.01.2026.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
-      <c r="B11" s="45" t="inlineStr">
+      <c r="B11" s="61" t="inlineStr">
         <is>
           <t>Quelle GJ 2025</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C11" s="62" t="inlineStr">
         <is>
           <t>Bericht über das Geschäftsjahr 2025 (Geschäftsbericht), ESWE Versorgungs AG – Bilanz S. 73, Gewinn- und Verlustrechnung S. 74, Kapitalflussrechnung und Investitionen S. 18, Umsatzaufteilung S. 16, Absatz S. 15, Verbindlichkeitenspiegel S. 82.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
-      <c r="B12" s="45" t="inlineStr">
+      <c r="B12" s="61" t="inlineStr">
         <is>
           <t>Darstellungseinheit</t>
         </is>
       </c>
-      <c r="C12" s="46" t="inlineStr">
+      <c r="C12" s="62" t="inlineStr">
         <is>
           <t>Die Abschlüsse werden in T€ veröffentlicht. In dieser Mappe sind sämtliche Beträge in EUR Mio. dargestellt, um dem Financial Model der evm AG / enm zu entsprechen. Die Werte sind exakt hinterlegt (T€ / 1.000) und lediglich auf eine Nachkommastelle gerundet angezeigt; alle Summen und Kontrollen rechnen mit den vollen Werten.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="B13" s="45" t="inlineStr">
+      <c r="B13" s="61" t="inlineStr">
         <is>
           <t>Farbkonvention</t>
         </is>
       </c>
-      <c r="C13" s="46" t="inlineStr">
+      <c r="C13" s="62" t="inlineStr">
         <is>
           <t>Blau = Eingabewert direkt aus dem Abschluss  |  Schwarz = Formel im Blatt  |  Grün = Verweis auf ein anderes Blatt  |  Grau kursiv = im betreffenden Jahr nicht separat ausgewiesen (n.a.).</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
-      <c r="B14" s="45" t="inlineStr">
+      <c r="B14" s="61" t="inlineStr">
         <is>
           <t>Abweichung 1</t>
         </is>
       </c>
-      <c r="C14" s="46" t="inlineStr">
+      <c r="C14" s="62" t="inlineStr">
         <is>
           <t>Kapitalflussrechnung 2022: Der JA 2022 nennt 95,4 / -44,9 / -23,5 Mio. €, der JA 2023 für dasselbe Jahr 78,0 / -34,0 / -17,0 Mio. €. Die Summe (27,0 Mio. €) ist in beiden Fassungen identisch – es handelt sich um eine Umgliederung zwischen den Cashflow-Bereichen. Angesetzt sind die Werte des JA 2023.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
-      <c r="B15" s="45" t="inlineStr">
+      <c r="B15" s="61" t="inlineStr">
         <is>
           <t>Abweichung 2</t>
         </is>
       </c>
-      <c r="C15" s="46" t="inlineStr">
+      <c r="C15" s="62" t="inlineStr">
         <is>
           <t>Verbindlichkeiten gegenüber Kreditinstituten 2025: Der Lagebericht (GB 2025 S. 20) nennt 123,7 Mio. €, der Verbindlichkeitenspiegel im Anhang (S. 82) 124.179 T€. Angesetzt ist der Anhangwert, da er mit der Summe der Verbindlichkeiten von 221.277 T€ in der Bilanz zusammenpasst.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="75" customHeight="1">
-      <c r="B16" s="45" t="inlineStr">
+      <c r="B16" s="61" t="inlineStr">
         <is>
           <t>Abweichung 3</t>
         </is>
       </c>
-      <c r="C16" s="46" t="inlineStr">
+      <c r="C16" s="62" t="inlineStr">
         <is>
           <t>Investitionen nach Unternehmensbereichen: Der JA 2024 weist eine eigene Zeile „Telekommunikation“ (2024: 1.259 T€; 2023: 919 T€) aus und nennt für 2023 abweichend vom JA 2023 Strom 524 statt 1.005 T€ und Sonstige 376 statt 814 T€. Der GB 2025 verzichtet auf die Zeile Telekommunikation und zeigt in der Vergleichsspalte 2024 Strom 1.259 und Sonstige 1.741 T€. Die Gesamtsummen (27.342 bzw. 27.453 T€) stimmen in allen Fassungen überein. Angesetzt ist jeweils die Darstellung des Berichtsjahres selbst.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1">
-      <c r="B17" s="45" t="inlineStr">
+      <c r="B17" s="61" t="inlineStr">
         <is>
           <t>Abweichung 4</t>
         </is>
       </c>
-      <c r="C17" s="46" t="inlineStr">
+      <c r="C17" s="62" t="inlineStr">
         <is>
           <t>Ergebnis vor Steuern: Der Lagebericht des GB 2025 nennt für 2025 52,4 Mio. € und für 2024 83,8 Mio. €. Diese Werte stammen aus der betriebswirtschaftlichen Kurzfassung der Ertragslage und weichen von der handelsrechtlichen GuV ab (52.650 bzw. 84.282 T€). Angesetzt sind durchgehend die Werte der GuV.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1">
-      <c r="B18" s="45" t="inlineStr">
+      <c r="B18" s="61" t="inlineStr">
         <is>
           <t>GuV-Gliederung</t>
         </is>
       </c>
-      <c r="C18" s="46" t="inlineStr">
+      <c r="C18" s="62" t="inlineStr">
         <is>
           <t>Die Positionsnummerierung folgt dem Jahresabschluss 2024. Die GuV 2025 kennt die Position „Einstellung in die anderen Gewinnrücklagen“ nicht; sie ist für 2025 mit null angesetzt, damit die Gliederung über alle fünf Jahre einheitlich ist.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="45" t="inlineStr">
+      <c r="B19" s="61" t="inlineStr">
         <is>
           <t>Kontrollen</t>
         </is>
       </c>
-      <c r="C19" s="46" t="inlineStr">
+      <c r="C19" s="62" t="inlineStr">
         <is>
           <t>Jedes Detailblatt enthält Kontrollzeilen, die auf null auflaufen müssen: Bilanz Aktiva ./. Passiva, Bilanzgewinn GuV ./. Bilanz, Finanzmittelfonds ./. Kassenbestand lt. Bilanz sowie Umsatzaufteilung ./. GuV.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="60" customHeight="1">
-      <c r="B20" s="45" t="inlineStr">
+      <c r="B20" s="61" t="inlineStr">
         <is>
           <t>Formatvorlage</t>
         </is>
       </c>
-      <c r="C20" s="46" t="inlineStr">
+      <c r="C20" s="62" t="inlineStr">
         <is>
           <t>Aufbau, Schriftart (Univers for Metzler), Schriftgrößen, Rahmen, Farben und Zahlenformate sind aus evm_enm_financial_model_2020_2024_v5 übernommen: Titelbanner weiß auf 003D7C, Kopfzeile weiß auf 3157E3, Zahlenformat #,##0.0 mit Klammern für negative Werte und „–“ für null, Prozente 0,0 %, Vielfache 0,0x, Spalte A als Randspalte, Kennzahlenblöcke durch dünne Linien getrennt.</t>
         </is>
@@ -1147,7 +1299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G46"/>
+  <dimension ref="B2:O55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1158,6 +1310,13 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="2" ht="21" customHeight="1">
@@ -1171,6 +1330,11 @@
       <c r="E2" s="1" t="n"/>
       <c r="F2" s="1" t="n"/>
       <c r="G2" s="1" t="n"/>
+      <c r="J2" s="15" t="inlineStr">
+        <is>
+          <t>Datenbereiche für Diagramme</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
@@ -1193,31 +1357,76 @@
       <c r="G3" s="6" t="n">
         <v>2025</v>
       </c>
+      <c r="J3" s="16" t="inlineStr">
+        <is>
+          <t>Ertragsentwicklung</t>
+        </is>
+      </c>
+      <c r="K3" s="17" t="n">
+        <v>2021</v>
+      </c>
+      <c r="L3" s="17" t="n">
+        <v>2022</v>
+      </c>
+      <c r="M3" s="17" t="n">
+        <v>2023</v>
+      </c>
+      <c r="N3" s="17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O3" s="18" t="n">
+        <v>2025</v>
+      </c>
     </row>
     <row r="4">
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Umsatzerlöse</t>
         </is>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="20">
         <f>'ESWE KPIs'!C5</f>
         <v/>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="20">
         <f>'ESWE KPIs'!D5</f>
         <v/>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="20">
         <f>'ESWE KPIs'!E5</f>
         <v/>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="20">
         <f>'ESWE KPIs'!F5</f>
         <v/>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="20">
         <f>'ESWE KPIs'!G5</f>
+        <v/>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t>Umsatzerlöse</t>
+        </is>
+      </c>
+      <c r="K4" s="22">
+        <f>C4</f>
+        <v/>
+      </c>
+      <c r="L4" s="22">
+        <f>D4</f>
+        <v/>
+      </c>
+      <c r="M4" s="22">
+        <f>E4</f>
+        <v/>
+      </c>
+      <c r="N4" s="22">
+        <f>F4</f>
+        <v/>
+      </c>
+      <c r="O4" s="23">
+        <f>G4</f>
         <v/>
       </c>
     </row>
@@ -1227,24 +1436,49 @@
           <t>Gesamtleistung</t>
         </is>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="24">
         <f>'ESWE KPIs'!C6</f>
         <v/>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="24">
         <f>'ESWE KPIs'!D6</f>
         <v/>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="24">
         <f>'ESWE KPIs'!E6</f>
         <v/>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="24">
         <f>'ESWE KPIs'!F6</f>
         <v/>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="24">
         <f>'ESWE KPIs'!G6</f>
+        <v/>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>Rohertrag</t>
+        </is>
+      </c>
+      <c r="K5" s="22">
+        <f>C6</f>
+        <v/>
+      </c>
+      <c r="L5" s="22">
+        <f>D6</f>
+        <v/>
+      </c>
+      <c r="M5" s="22">
+        <f>E6</f>
+        <v/>
+      </c>
+      <c r="N5" s="22">
+        <f>F6</f>
+        <v/>
+      </c>
+      <c r="O5" s="23">
+        <f>G6</f>
         <v/>
       </c>
     </row>
@@ -1254,24 +1488,49 @@
           <t>Rohertrag</t>
         </is>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="24">
         <f>'ESWE KPIs'!C7</f>
         <v/>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="24">
         <f>'ESWE KPIs'!D7</f>
         <v/>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="24">
         <f>'ESWE KPIs'!E7</f>
         <v/>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="24">
         <f>'ESWE KPIs'!F7</f>
         <v/>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="24">
         <f>'ESWE KPIs'!G7</f>
+        <v/>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="K6" s="22">
+        <f>C8</f>
+        <v/>
+      </c>
+      <c r="L6" s="22">
+        <f>D8</f>
+        <v/>
+      </c>
+      <c r="M6" s="22">
+        <f>E8</f>
+        <v/>
+      </c>
+      <c r="N6" s="22">
+        <f>F8</f>
+        <v/>
+      </c>
+      <c r="O6" s="23">
+        <f>G8</f>
         <v/>
       </c>
     </row>
@@ -1281,51 +1540,101 @@
           <t>Rohertragsmarge</t>
         </is>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="25">
         <f>'ESWE KPIs'!C8</f>
         <v/>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="25">
         <f>'ESWE KPIs'!D8</f>
         <v/>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="25">
         <f>'ESWE KPIs'!E8</f>
         <v/>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="25">
         <f>'ESWE KPIs'!F8</f>
         <v/>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="25">
         <f>'ESWE KPIs'!G8</f>
         <v/>
       </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>Betriebliches Ergebnis</t>
+        </is>
+      </c>
+      <c r="K7" s="22">
+        <f>C9</f>
+        <v/>
+      </c>
+      <c r="L7" s="22">
+        <f>D9</f>
+        <v/>
+      </c>
+      <c r="M7" s="22">
+        <f>E9</f>
+        <v/>
+      </c>
+      <c r="N7" s="22">
+        <f>F9</f>
+        <v/>
+      </c>
+      <c r="O7" s="23">
+        <f>G9</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="20">
         <f>'ESWE KPIs'!C10</f>
         <v/>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="20">
         <f>'ESWE KPIs'!D10</f>
         <v/>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="20">
         <f>'ESWE KPIs'!E10</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="20">
         <f>'ESWE KPIs'!F10</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="20">
         <f>'ESWE KPIs'!G10</f>
+        <v/>
+      </c>
+      <c r="J8" s="26" t="inlineStr">
+        <is>
+          <t>Jahresüberschuss</t>
+        </is>
+      </c>
+      <c r="K8" s="27">
+        <f>C12</f>
+        <v/>
+      </c>
+      <c r="L8" s="27">
+        <f>D12</f>
+        <v/>
+      </c>
+      <c r="M8" s="27">
+        <f>E12</f>
+        <v/>
+      </c>
+      <c r="N8" s="27">
+        <f>F12</f>
+        <v/>
+      </c>
+      <c r="O8" s="28">
+        <f>G12</f>
         <v/>
       </c>
     </row>
@@ -1335,23 +1644,23 @@
           <t>Betriebliches Ergebnis</t>
         </is>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="24">
         <f>'ESWE KPIs'!C11</f>
         <v/>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="24">
         <f>'ESWE KPIs'!D11</f>
         <v/>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="24">
         <f>'ESWE KPIs'!E11</f>
         <v/>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="24">
         <f>'ESWE KPIs'!F11</f>
         <v/>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="24">
         <f>'ESWE KPIs'!G11</f>
         <v/>
       </c>
@@ -1362,25 +1671,45 @@
           <t>Beteiligungsergebnis</t>
         </is>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="24">
         <f>'ESWE KPIs'!C12</f>
         <v/>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="24">
         <f>'ESWE KPIs'!D12</f>
         <v/>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="24">
         <f>'ESWE KPIs'!E12</f>
         <v/>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="24">
         <f>'ESWE KPIs'!F12</f>
         <v/>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="24">
         <f>'ESWE KPIs'!G12</f>
         <v/>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>2021</v>
+      </c>
+      <c r="L10" s="17" t="n">
+        <v>2022</v>
+      </c>
+      <c r="M10" s="17" t="n">
+        <v>2023</v>
+      </c>
+      <c r="N10" s="17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O10" s="18" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="11">
@@ -1389,51 +1718,128 @@
           <t>Ergebnis vor Steuern</t>
         </is>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="29">
         <f>'ESWE KPIs'!C14</f>
         <v/>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="29">
         <f>'ESWE KPIs'!D14</f>
         <v/>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="29">
         <f>'ESWE KPIs'!E14</f>
         <v/>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="29">
         <f>'ESWE KPIs'!F14</f>
         <v/>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="29">
         <f>'ESWE KPIs'!G14</f>
         <v/>
       </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>Operating Cash Flow</t>
+        </is>
+      </c>
+      <c r="K11" s="22">
+        <f>C15</f>
+        <v/>
+      </c>
+      <c r="L11" s="22">
+        <f>D15</f>
+        <v/>
+      </c>
+      <c r="M11" s="22">
+        <f>E15</f>
+        <v/>
+      </c>
+      <c r="N11" s="22">
+        <f>F15</f>
+        <v/>
+      </c>
+      <c r="O11" s="23">
+        <f>G15</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Jahresüberschuss</t>
         </is>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="20">
         <f>'ESWE KPIs'!C15</f>
         <v/>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="20">
         <f>'ESWE KPIs'!D15</f>
         <v/>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="20">
         <f>'ESWE KPIs'!E15</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="20">
         <f>'ESWE KPIs'!F15</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="20">
         <f>'ESWE KPIs'!G15</f>
+        <v/>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>Investing Cash Flow</t>
+        </is>
+      </c>
+      <c r="K12" s="22">
+        <f>C16</f>
+        <v/>
+      </c>
+      <c r="L12" s="22">
+        <f>D16</f>
+        <v/>
+      </c>
+      <c r="M12" s="22">
+        <f>E16</f>
+        <v/>
+      </c>
+      <c r="N12" s="22">
+        <f>F16</f>
+        <v/>
+      </c>
+      <c r="O12" s="23">
+        <f>G16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>Financing Cash Flow</t>
+        </is>
+      </c>
+      <c r="K13" s="22">
+        <f>C17</f>
+        <v/>
+      </c>
+      <c r="L13" s="22">
+        <f>D17</f>
+        <v/>
+      </c>
+      <c r="M13" s="22">
+        <f>E17</f>
+        <v/>
+      </c>
+      <c r="N13" s="22">
+        <f>F17</f>
+        <v/>
+      </c>
+      <c r="O13" s="23">
+        <f>G17</f>
         <v/>
       </c>
     </row>
@@ -1458,6 +1864,31 @@
       <c r="G14" s="6" t="n">
         <v>2025</v>
       </c>
+      <c r="J14" s="26" t="inlineStr">
+        <is>
+          <t>Cashflow gesamt</t>
+        </is>
+      </c>
+      <c r="K14" s="27">
+        <f>C18</f>
+        <v/>
+      </c>
+      <c r="L14" s="27">
+        <f>D18</f>
+        <v/>
+      </c>
+      <c r="M14" s="27">
+        <f>E18</f>
+        <v/>
+      </c>
+      <c r="N14" s="27">
+        <f>F18</f>
+        <v/>
+      </c>
+      <c r="O14" s="28">
+        <f>G18</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="8" t="inlineStr">
@@ -1465,23 +1896,23 @@
           <t>Operating Cash Flow</t>
         </is>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="24">
         <f>'ESWE KPIs'!C17</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="24">
         <f>'ESWE KPIs'!D17</f>
         <v/>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="24">
         <f>'ESWE KPIs'!E17</f>
         <v/>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="24">
         <f>'ESWE KPIs'!F17</f>
         <v/>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="24">
         <f>'ESWE KPIs'!G17</f>
         <v/>
       </c>
@@ -1492,51 +1923,96 @@
           <t>Investing Cash Flow</t>
         </is>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="24">
         <f>'ESWE KPIs'!C18</f>
         <v/>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="24">
         <f>'ESWE KPIs'!D18</f>
         <v/>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="24">
         <f>'ESWE KPIs'!E18</f>
         <v/>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="24">
         <f>'ESWE KPIs'!F18</f>
         <v/>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="24">
         <f>'ESWE KPIs'!G18</f>
         <v/>
       </c>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>Verschuldung</t>
+        </is>
+      </c>
+      <c r="K16" s="17" t="n">
+        <v>2021</v>
+      </c>
+      <c r="L16" s="17" t="n">
+        <v>2022</v>
+      </c>
+      <c r="M16" s="17" t="n">
+        <v>2023</v>
+      </c>
+      <c r="N16" s="17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O16" s="18" t="n">
+        <v>2025</v>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>Financing Cash Flow</t>
         </is>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="31">
         <f>'ESWE KPIs'!C19</f>
         <v/>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="31">
         <f>'ESWE KPIs'!D19</f>
         <v/>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="31">
         <f>'ESWE KPIs'!E19</f>
         <v/>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="31">
         <f>'ESWE KPIs'!F19</f>
         <v/>
       </c>
-      <c r="G17" s="21">
+      <c r="G17" s="31">
         <f>'ESWE KPIs'!G19</f>
+        <v/>
+      </c>
+      <c r="J17" s="21" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="K17" s="22">
+        <f>C26</f>
+        <v/>
+      </c>
+      <c r="L17" s="22">
+        <f>D26</f>
+        <v/>
+      </c>
+      <c r="M17" s="22">
+        <f>E26</f>
+        <v/>
+      </c>
+      <c r="N17" s="22">
+        <f>F26</f>
+        <v/>
+      </c>
+      <c r="O17" s="23">
+        <f>G26</f>
         <v/>
       </c>
     </row>
@@ -1546,24 +2022,49 @@
           <t>Cashflow gesamt</t>
         </is>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="32">
         <f>SUM(C15:C17)</f>
         <v/>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="32">
         <f>SUM(D15:D17)</f>
         <v/>
       </c>
-      <c r="E18" s="22">
+      <c r="E18" s="32">
         <f>SUM(E15:E17)</f>
         <v/>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="32">
         <f>SUM(F15:F17)</f>
         <v/>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="32">
         <f>SUM(G15:G17)</f>
+        <v/>
+      </c>
+      <c r="J18" s="26" t="inlineStr">
+        <is>
+          <t>Net Debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="K18" s="33">
+        <f>C27</f>
+        <v/>
+      </c>
+      <c r="L18" s="33">
+        <f>D27</f>
+        <v/>
+      </c>
+      <c r="M18" s="33">
+        <f>E27</f>
+        <v/>
+      </c>
+      <c r="N18" s="33">
+        <f>F27</f>
+        <v/>
+      </c>
+      <c r="O18" s="34">
+        <f>G27</f>
         <v/>
       </c>
     </row>
@@ -1588,6 +2089,26 @@
       <c r="G20" s="6" t="n">
         <v>2025</v>
       </c>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>Bilanz- und Finanzstruktur</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="n">
+        <v>2021</v>
+      </c>
+      <c r="L20" s="17" t="n">
+        <v>2022</v>
+      </c>
+      <c r="M20" s="17" t="n">
+        <v>2023</v>
+      </c>
+      <c r="N20" s="17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O20" s="18" t="n">
+        <v>2025</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="8" t="inlineStr">
@@ -1595,24 +2116,49 @@
           <t>Bilanzsumme</t>
         </is>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="24">
         <f>'ESWE KPIs'!C22</f>
         <v/>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="24">
         <f>'ESWE KPIs'!D22</f>
         <v/>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="24">
         <f>'ESWE KPIs'!E22</f>
         <v/>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="24">
         <f>'ESWE KPIs'!F22</f>
         <v/>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="24">
         <f>'ESWE KPIs'!G22</f>
+        <v/>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>Liquide Mittel</t>
+        </is>
+      </c>
+      <c r="K21" s="22">
+        <f>C24</f>
+        <v/>
+      </c>
+      <c r="L21" s="22">
+        <f>D24</f>
+        <v/>
+      </c>
+      <c r="M21" s="22">
+        <f>E24</f>
+        <v/>
+      </c>
+      <c r="N21" s="22">
+        <f>F24</f>
+        <v/>
+      </c>
+      <c r="O21" s="23">
+        <f>G24</f>
         <v/>
       </c>
     </row>
@@ -1622,51 +2168,101 @@
           <t>Eigenkapital</t>
         </is>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="24">
         <f>'ESWE KPIs'!C23</f>
         <v/>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="24">
         <f>'ESWE KPIs'!D23</f>
         <v/>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="24">
         <f>'ESWE KPIs'!E23</f>
         <v/>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="24">
         <f>'ESWE KPIs'!F23</f>
         <v/>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="24">
         <f>'ESWE KPIs'!G23</f>
         <v/>
       </c>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="K22" s="22">
+        <f>C26</f>
+        <v/>
+      </c>
+      <c r="L22" s="22">
+        <f>D26</f>
+        <v/>
+      </c>
+      <c r="M22" s="22">
+        <f>E26</f>
+        <v/>
+      </c>
+      <c r="N22" s="22">
+        <f>F26</f>
+        <v/>
+      </c>
+      <c r="O22" s="23">
+        <f>G26</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>Eigenkapitalquote</t>
         </is>
       </c>
-      <c r="C23" s="23">
+      <c r="C23" s="35">
         <f>'ESWE KPIs'!C24</f>
         <v/>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="35">
         <f>'ESWE KPIs'!D24</f>
         <v/>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="35">
         <f>'ESWE KPIs'!E24</f>
         <v/>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="35">
         <f>'ESWE KPIs'!F24</f>
         <v/>
       </c>
-      <c r="G23" s="23">
+      <c r="G23" s="35">
         <f>'ESWE KPIs'!G24</f>
+        <v/>
+      </c>
+      <c r="J23" s="26" t="inlineStr">
+        <is>
+          <t>Eigenkapitalquote</t>
+        </is>
+      </c>
+      <c r="K23" s="36">
+        <f>C23</f>
+        <v/>
+      </c>
+      <c r="L23" s="36">
+        <f>D23</f>
+        <v/>
+      </c>
+      <c r="M23" s="36">
+        <f>E23</f>
+        <v/>
+      </c>
+      <c r="N23" s="36">
+        <f>F23</f>
+        <v/>
+      </c>
+      <c r="O23" s="37">
+        <f>G23</f>
         <v/>
       </c>
     </row>
@@ -1676,23 +2272,23 @@
           <t>Kassenbestand</t>
         </is>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="24">
         <f>'ESWE KPIs'!C27</f>
         <v/>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="24">
         <f>'ESWE KPIs'!D27</f>
         <v/>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="24">
         <f>'ESWE KPIs'!E27</f>
         <v/>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="24">
         <f>'ESWE KPIs'!F27</f>
         <v/>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="24">
         <f>'ESWE KPIs'!G27</f>
         <v/>
       </c>
@@ -1703,25 +2299,45 @@
           <t>Finanzverbindlichkeiten</t>
         </is>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="24">
         <f>'ESWE KPIs'!C28</f>
         <v/>
       </c>
-      <c r="D25" s="17">
+      <c r="D25" s="24">
         <f>'ESWE KPIs'!D28</f>
         <v/>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="24">
         <f>'ESWE KPIs'!E28</f>
         <v/>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="24">
         <f>'ESWE KPIs'!F28</f>
         <v/>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="24">
         <f>'ESWE KPIs'!G28</f>
         <v/>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>Investitionen</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="n">
+        <v>2021</v>
+      </c>
+      <c r="L25" s="17" t="n">
+        <v>2022</v>
+      </c>
+      <c r="M25" s="17" t="n">
+        <v>2023</v>
+      </c>
+      <c r="N25" s="17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O25" s="18" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="26">
@@ -1730,79 +2346,139 @@
           <t>Net Debt</t>
         </is>
       </c>
-      <c r="C26" s="19">
+      <c r="C26" s="29">
         <f>'ESWE KPIs'!C29</f>
         <v/>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="29">
         <f>'ESWE KPIs'!D29</f>
         <v/>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="29">
         <f>'ESWE KPIs'!E29</f>
         <v/>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="29">
         <f>'ESWE KPIs'!F29</f>
         <v/>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="29">
         <f>'ESWE KPIs'!G29</f>
         <v/>
       </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>Gesamtinvestitionen</t>
+        </is>
+      </c>
+      <c r="K26" s="22">
+        <f>C28</f>
+        <v/>
+      </c>
+      <c r="L26" s="22">
+        <f>D28</f>
+        <v/>
+      </c>
+      <c r="M26" s="22">
+        <f>E28</f>
+        <v/>
+      </c>
+      <c r="N26" s="22">
+        <f>F28</f>
+        <v/>
+      </c>
+      <c r="O26" s="23">
+        <f>G28</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>Net Debt / EBITDA</t>
         </is>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="38">
         <f>'ESWE KPIs'!C30</f>
         <v/>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="38">
         <f>'ESWE KPIs'!D30</f>
         <v/>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="38">
         <f>'ESWE KPIs'!E30</f>
         <v/>
       </c>
-      <c r="F27" s="24">
+      <c r="F27" s="38">
         <f>'ESWE KPIs'!F30</f>
         <v/>
       </c>
-      <c r="G27" s="24">
+      <c r="G27" s="38">
         <f>'ESWE KPIs'!G30</f>
         <v/>
       </c>
+      <c r="J27" s="26" t="inlineStr">
+        <is>
+          <t>Investitionen / Umsatz</t>
+        </is>
+      </c>
+      <c r="K27" s="36">
+        <f>'ESWE KPIs'!C33</f>
+        <v/>
+      </c>
+      <c r="L27" s="36">
+        <f>'ESWE KPIs'!D33</f>
+        <v/>
+      </c>
+      <c r="M27" s="36">
+        <f>'ESWE KPIs'!E33</f>
+        <v/>
+      </c>
+      <c r="N27" s="36">
+        <f>'ESWE KPIs'!F33</f>
+        <v/>
+      </c>
+      <c r="O27" s="37">
+        <f>'ESWE KPIs'!G33</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>Capex (Gesamtinvestitionen)</t>
         </is>
       </c>
-      <c r="C28" s="16">
+      <c r="C28" s="20">
         <f>'ESWE KPIs'!C32</f>
         <v/>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="20">
         <f>'ESWE KPIs'!D32</f>
         <v/>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="20">
         <f>'ESWE KPIs'!E32</f>
         <v/>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="20">
         <f>'ESWE KPIs'!F32</f>
         <v/>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="20">
         <f>'ESWE KPIs'!G32</f>
         <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>Umsatz nach Geschäftsfeldern 2025</t>
+        </is>
+      </c>
+      <c r="K29" s="18" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="30">
@@ -1826,6 +2502,15 @@
       <c r="G30" s="6" t="n">
         <v>2025</v>
       </c>
+      <c r="J30" s="21" t="inlineStr">
+        <is>
+          <t>Stromversorgung (inkl. Handel)</t>
+        </is>
+      </c>
+      <c r="K30" s="23">
+        <f>G31</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="B31" s="8" t="inlineStr">
@@ -1833,24 +2518,33 @@
           <t>Stromversorgung (inkl. Handelsgeschäfte)</t>
         </is>
       </c>
-      <c r="C31" s="17">
-        <f>'ESWE Capex Revenue'!C7</f>
-        <v/>
-      </c>
-      <c r="D31" s="17">
-        <f>'ESWE Capex Revenue'!D7</f>
-        <v/>
-      </c>
-      <c r="E31" s="17">
-        <f>'ESWE Capex Revenue'!E7</f>
-        <v/>
-      </c>
-      <c r="F31" s="17">
-        <f>'ESWE Capex Revenue'!F7</f>
-        <v/>
-      </c>
-      <c r="G31" s="17">
-        <f>'ESWE Capex Revenue'!G7</f>
+      <c r="C31" s="24">
+        <f>'ESWE Capex Revenue'!C24</f>
+        <v/>
+      </c>
+      <c r="D31" s="24">
+        <f>'ESWE Capex Revenue'!D24</f>
+        <v/>
+      </c>
+      <c r="E31" s="24">
+        <f>'ESWE Capex Revenue'!E24</f>
+        <v/>
+      </c>
+      <c r="F31" s="24">
+        <f>'ESWE Capex Revenue'!F24</f>
+        <v/>
+      </c>
+      <c r="G31" s="24">
+        <f>'ESWE Capex Revenue'!G24</f>
+        <v/>
+      </c>
+      <c r="J31" s="21" t="inlineStr">
+        <is>
+          <t>Gasversorgung (inkl. Handel)</t>
+        </is>
+      </c>
+      <c r="K31" s="23">
+        <f>G32</f>
         <v/>
       </c>
     </row>
@@ -1860,24 +2554,33 @@
           <t>Gasversorgung (inkl. Handelsgeschäfte)</t>
         </is>
       </c>
-      <c r="C32" s="17">
-        <f>'ESWE Capex Revenue'!C8</f>
-        <v/>
-      </c>
-      <c r="D32" s="17">
-        <f>'ESWE Capex Revenue'!D8</f>
-        <v/>
-      </c>
-      <c r="E32" s="17">
-        <f>'ESWE Capex Revenue'!E8</f>
-        <v/>
-      </c>
-      <c r="F32" s="17">
-        <f>'ESWE Capex Revenue'!F8</f>
-        <v/>
-      </c>
-      <c r="G32" s="17">
-        <f>'ESWE Capex Revenue'!G8</f>
+      <c r="C32" s="24">
+        <f>'ESWE Capex Revenue'!C25</f>
+        <v/>
+      </c>
+      <c r="D32" s="24">
+        <f>'ESWE Capex Revenue'!D25</f>
+        <v/>
+      </c>
+      <c r="E32" s="24">
+        <f>'ESWE Capex Revenue'!E25</f>
+        <v/>
+      </c>
+      <c r="F32" s="24">
+        <f>'ESWE Capex Revenue'!F25</f>
+        <v/>
+      </c>
+      <c r="G32" s="24">
+        <f>'ESWE Capex Revenue'!G25</f>
+        <v/>
+      </c>
+      <c r="J32" s="21" t="inlineStr">
+        <is>
+          <t>Wärmeversorgung</t>
+        </is>
+      </c>
+      <c r="K32" s="23">
+        <f>G33</f>
         <v/>
       </c>
     </row>
@@ -1887,24 +2590,33 @@
           <t>Wärmeversorgung</t>
         </is>
       </c>
-      <c r="C33" s="17">
-        <f>'ESWE Capex Revenue'!C9</f>
-        <v/>
-      </c>
-      <c r="D33" s="17">
-        <f>'ESWE Capex Revenue'!D9</f>
-        <v/>
-      </c>
-      <c r="E33" s="17">
-        <f>'ESWE Capex Revenue'!E9</f>
-        <v/>
-      </c>
-      <c r="F33" s="17">
-        <f>'ESWE Capex Revenue'!F9</f>
-        <v/>
-      </c>
-      <c r="G33" s="17">
-        <f>'ESWE Capex Revenue'!G9</f>
+      <c r="C33" s="24">
+        <f>'ESWE Capex Revenue'!C26</f>
+        <v/>
+      </c>
+      <c r="D33" s="24">
+        <f>'ESWE Capex Revenue'!D26</f>
+        <v/>
+      </c>
+      <c r="E33" s="24">
+        <f>'ESWE Capex Revenue'!E26</f>
+        <v/>
+      </c>
+      <c r="F33" s="24">
+        <f>'ESWE Capex Revenue'!F26</f>
+        <v/>
+      </c>
+      <c r="G33" s="24">
+        <f>'ESWE Capex Revenue'!G26</f>
+        <v/>
+      </c>
+      <c r="J33" s="21" t="inlineStr">
+        <is>
+          <t>Betriebsführung Wasserversorgung</t>
+        </is>
+      </c>
+      <c r="K33" s="23">
+        <f>G34</f>
         <v/>
       </c>
     </row>
@@ -1914,24 +2626,33 @@
           <t>Betriebsführung Wasserversorgung</t>
         </is>
       </c>
-      <c r="C34" s="17">
-        <f>'ESWE Capex Revenue'!C10</f>
-        <v/>
-      </c>
-      <c r="D34" s="17">
-        <f>'ESWE Capex Revenue'!D10</f>
-        <v/>
-      </c>
-      <c r="E34" s="17">
-        <f>'ESWE Capex Revenue'!E10</f>
-        <v/>
-      </c>
-      <c r="F34" s="17">
-        <f>'ESWE Capex Revenue'!F10</f>
-        <v/>
-      </c>
-      <c r="G34" s="17">
-        <f>'ESWE Capex Revenue'!G10</f>
+      <c r="C34" s="24">
+        <f>'ESWE Capex Revenue'!C27</f>
+        <v/>
+      </c>
+      <c r="D34" s="24">
+        <f>'ESWE Capex Revenue'!D27</f>
+        <v/>
+      </c>
+      <c r="E34" s="24">
+        <f>'ESWE Capex Revenue'!E27</f>
+        <v/>
+      </c>
+      <c r="F34" s="24">
+        <f>'ESWE Capex Revenue'!F27</f>
+        <v/>
+      </c>
+      <c r="G34" s="24">
+        <f>'ESWE Capex Revenue'!G27</f>
+        <v/>
+      </c>
+      <c r="J34" s="21" t="inlineStr">
+        <is>
+          <t>Wasserverkauf an WLW</t>
+        </is>
+      </c>
+      <c r="K34" s="23">
+        <f>G35</f>
         <v/>
       </c>
     </row>
@@ -1941,24 +2662,33 @@
           <t>Wasserverkauf an WLW</t>
         </is>
       </c>
-      <c r="C35" s="17">
-        <f>'ESWE Capex Revenue'!C11</f>
-        <v/>
-      </c>
-      <c r="D35" s="17">
-        <f>'ESWE Capex Revenue'!D11</f>
-        <v/>
-      </c>
-      <c r="E35" s="17">
-        <f>'ESWE Capex Revenue'!E11</f>
-        <v/>
-      </c>
-      <c r="F35" s="17">
-        <f>'ESWE Capex Revenue'!F11</f>
-        <v/>
-      </c>
-      <c r="G35" s="17">
-        <f>'ESWE Capex Revenue'!G11</f>
+      <c r="C35" s="24">
+        <f>'ESWE Capex Revenue'!C28</f>
+        <v/>
+      </c>
+      <c r="D35" s="24">
+        <f>'ESWE Capex Revenue'!D28</f>
+        <v/>
+      </c>
+      <c r="E35" s="24">
+        <f>'ESWE Capex Revenue'!E28</f>
+        <v/>
+      </c>
+      <c r="F35" s="24">
+        <f>'ESWE Capex Revenue'!F28</f>
+        <v/>
+      </c>
+      <c r="G35" s="24">
+        <f>'ESWE Capex Revenue'!G28</f>
+        <v/>
+      </c>
+      <c r="J35" s="21" t="inlineStr">
+        <is>
+          <t>Konzerninterne Dienstleistungen</t>
+        </is>
+      </c>
+      <c r="K35" s="23">
+        <f>G36</f>
         <v/>
       </c>
     </row>
@@ -1968,24 +2698,33 @@
           <t>Konzerninterne Dienstleistungen</t>
         </is>
       </c>
-      <c r="C36" s="17">
-        <f>'ESWE Capex Revenue'!C12</f>
-        <v/>
-      </c>
-      <c r="D36" s="17">
-        <f>'ESWE Capex Revenue'!D12</f>
-        <v/>
-      </c>
-      <c r="E36" s="17">
-        <f>'ESWE Capex Revenue'!E12</f>
-        <v/>
-      </c>
-      <c r="F36" s="17">
-        <f>'ESWE Capex Revenue'!F12</f>
-        <v/>
-      </c>
-      <c r="G36" s="17">
-        <f>'ESWE Capex Revenue'!G12</f>
+      <c r="C36" s="24">
+        <f>'ESWE Capex Revenue'!C29</f>
+        <v/>
+      </c>
+      <c r="D36" s="24">
+        <f>'ESWE Capex Revenue'!D29</f>
+        <v/>
+      </c>
+      <c r="E36" s="24">
+        <f>'ESWE Capex Revenue'!E29</f>
+        <v/>
+      </c>
+      <c r="F36" s="24">
+        <f>'ESWE Capex Revenue'!F29</f>
+        <v/>
+      </c>
+      <c r="G36" s="24">
+        <f>'ESWE Capex Revenue'!G29</f>
+        <v/>
+      </c>
+      <c r="J36" s="26" t="inlineStr">
+        <is>
+          <t>Übrige Umsatzerlöse</t>
+        </is>
+      </c>
+      <c r="K36" s="28">
+        <f>G37</f>
         <v/>
       </c>
     </row>
@@ -1995,51 +2734,70 @@
           <t>Übrige Umsatzerlöse</t>
         </is>
       </c>
-      <c r="C37" s="17">
-        <f>'ESWE Capex Revenue'!C13</f>
-        <v/>
-      </c>
-      <c r="D37" s="17">
-        <f>'ESWE Capex Revenue'!D13</f>
-        <v/>
-      </c>
-      <c r="E37" s="17">
-        <f>'ESWE Capex Revenue'!E13</f>
-        <v/>
-      </c>
-      <c r="F37" s="17">
-        <f>'ESWE Capex Revenue'!F13</f>
-        <v/>
-      </c>
-      <c r="G37" s="17">
-        <f>'ESWE Capex Revenue'!G13</f>
+      <c r="C37" s="24">
+        <f>'ESWE Capex Revenue'!C30</f>
+        <v/>
+      </c>
+      <c r="D37" s="24">
+        <f>'ESWE Capex Revenue'!D30</f>
+        <v/>
+      </c>
+      <c r="E37" s="24">
+        <f>'ESWE Capex Revenue'!E30</f>
+        <v/>
+      </c>
+      <c r="F37" s="24">
+        <f>'ESWE Capex Revenue'!F30</f>
+        <v/>
+      </c>
+      <c r="G37" s="24">
+        <f>'ESWE Capex Revenue'!G30</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="25" t="inlineStr">
+      <c r="B38" s="39" t="inlineStr">
         <is>
           <t>Umsätze lt. GuV</t>
         </is>
       </c>
-      <c r="C38" s="26">
+      <c r="C38" s="40">
         <f>SUM(C31:C37)</f>
         <v/>
       </c>
-      <c r="D38" s="26">
+      <c r="D38" s="40">
         <f>SUM(D31:D37)</f>
         <v/>
       </c>
-      <c r="E38" s="26">
+      <c r="E38" s="40">
         <f>SUM(E31:E37)</f>
         <v/>
       </c>
-      <c r="F38" s="26">
+      <c r="F38" s="40">
         <f>SUM(F31:F37)</f>
         <v/>
       </c>
-      <c r="G38" s="26">
+      <c r="G38" s="40">
         <f>SUM(G31:G37)</f>
+        <v/>
+      </c>
+      <c r="J38" s="16" t="inlineStr">
+        <is>
+          <t>Investitionen nach Geschäftsfeldern 2025</t>
+        </is>
+      </c>
+      <c r="K38" s="18" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="J39" s="21" t="inlineStr">
+        <is>
+          <t>Stromversorgung</t>
+        </is>
+      </c>
+      <c r="K39" s="23">
+        <f>'ESWE Capex Revenue'!G6</f>
         <v/>
       </c>
     </row>
@@ -2049,24 +2807,44 @@
           <t>Anteil Strom / Gas am Umsatz</t>
         </is>
       </c>
-      <c r="C40" s="27">
+      <c r="C40" s="41">
         <f>IFERROR((C31+C32)/C38,0)</f>
         <v/>
       </c>
-      <c r="D40" s="27">
+      <c r="D40" s="41">
         <f>IFERROR((D31+D32)/D38,0)</f>
         <v/>
       </c>
-      <c r="E40" s="27">
+      <c r="E40" s="41">
         <f>IFERROR((E31+E32)/E38,0)</f>
         <v/>
       </c>
-      <c r="F40" s="27">
+      <c r="F40" s="41">
         <f>IFERROR((F31+F32)/F38,0)</f>
         <v/>
       </c>
-      <c r="G40" s="27">
+      <c r="G40" s="41">
         <f>IFERROR((G31+G32)/G38,0)</f>
+        <v/>
+      </c>
+      <c r="J40" s="21" t="inlineStr">
+        <is>
+          <t>Gasversorgung</t>
+        </is>
+      </c>
+      <c r="K40" s="23">
+        <f>'ESWE Capex Revenue'!G7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="J41" s="21" t="inlineStr">
+        <is>
+          <t>Wasserversorgung</t>
+        </is>
+      </c>
+      <c r="K41" s="23">
+        <f>'ESWE Capex Revenue'!G8</f>
         <v/>
       </c>
     </row>
@@ -2076,18 +2854,197 @@
           <t>Methodik: Net Debt = Verbindlichkeiten gegenüber Kreditinstituten abzüglich Kassenbestand und Guthaben bei Kreditinstituten. Intercompany-Finanzierungen, empfangene Ertragszuschüsse und Rückstellungen sind nicht einbezogen, da eine belastbare Trennung von operativen und finanzierungsbezogenen Positionen aus dem veröffentlichten Einzelabschluss nicht durchgängig möglich ist. Gesamtleistung = Umsatzerlöse zzgl. Bestandsveränderung und anderer aktivierter Eigenleistungen. Rohertrag = Gesamtleistung abzüglich Materialaufwand. EBITDA = Betriebliches Ergebnis zzgl. Abschreibungen auf immaterielle Vermögensgegenstände und Sachanlagen. Sämtliche Werte dieses Blattes sind Verweise (grün) auf die Detailblätter.</t>
         </is>
       </c>
-    </row>
-    <row r="43"/>
+      <c r="J42" s="21" t="inlineStr">
+        <is>
+          <t>Wärmeversorgung</t>
+        </is>
+      </c>
+      <c r="K42" s="23">
+        <f>'ESWE Capex Revenue'!G9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="J43" s="21" t="inlineStr">
+        <is>
+          <t>Sonstige Bereiche</t>
+        </is>
+      </c>
+      <c r="K43" s="23">
+        <f>'ESWE Capex Revenue'!G11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="J44" s="21" t="inlineStr">
+        <is>
+          <t>Gemeinsame Bereiche</t>
+        </is>
+      </c>
+      <c r="K44" s="23">
+        <f>'ESWE Capex Revenue'!G12</f>
+        <v/>
+      </c>
+    </row>
     <row r="45">
       <c r="B45" s="14" t="inlineStr">
         <is>
           <t>Die Umsatzaufteilung folgt der im Geschäftsbericht 2025 verwendeten siebenzeiligen Gliederung. Für 2021 bis 2024 wurden die in den Jahresabschlüssen separat ausgewiesenen Positionen entsprechend zusammengefasst (Strom- und Gashandel in die jeweilige Sparte, Tankstelle und Auflösung empfangener Ertragszuschüsse in die übrigen Umsatzerlöse). Siehe Blatt „Quellen &amp; Hinweise“.</t>
         </is>
       </c>
+      <c r="J45" s="26" t="inlineStr">
+        <is>
+          <t>Beteiligungen (Finanzanlagen)</t>
+        </is>
+      </c>
+      <c r="K45" s="28">
+        <f>'ESWE Capex Revenue'!G13</f>
+        <v/>
+      </c>
     </row>
     <row r="46"/>
+    <row r="47">
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>Absatzmengen</t>
+        </is>
+      </c>
+      <c r="K47" s="17" t="n">
+        <v>2021</v>
+      </c>
+      <c r="L47" s="17" t="n">
+        <v>2022</v>
+      </c>
+      <c r="M47" s="17" t="n">
+        <v>2023</v>
+      </c>
+      <c r="N47" s="17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O47" s="18" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="J48" s="21" t="inlineStr">
+        <is>
+          <t>Strom (Mio. kWh)</t>
+        </is>
+      </c>
+      <c r="K48" s="42">
+        <f>'ESWE KPIs'!C36</f>
+        <v/>
+      </c>
+      <c r="L48" s="42">
+        <f>'ESWE KPIs'!D36</f>
+        <v/>
+      </c>
+      <c r="M48" s="42">
+        <f>'ESWE KPIs'!E36</f>
+        <v/>
+      </c>
+      <c r="N48" s="42">
+        <f>'ESWE KPIs'!F36</f>
+        <v/>
+      </c>
+      <c r="O48" s="43">
+        <f>'ESWE KPIs'!G36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="J49" s="21" t="inlineStr">
+        <is>
+          <t>Gas (Mio. kWh)</t>
+        </is>
+      </c>
+      <c r="K49" s="42">
+        <f>'ESWE KPIs'!C37</f>
+        <v/>
+      </c>
+      <c r="L49" s="42">
+        <f>'ESWE KPIs'!D37</f>
+        <v/>
+      </c>
+      <c r="M49" s="42">
+        <f>'ESWE KPIs'!E37</f>
+        <v/>
+      </c>
+      <c r="N49" s="42">
+        <f>'ESWE KPIs'!F37</f>
+        <v/>
+      </c>
+      <c r="O49" s="43">
+        <f>'ESWE KPIs'!G37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="J50" s="21" t="inlineStr">
+        <is>
+          <t>Wärme / Kälte (Mio. kWh)</t>
+        </is>
+      </c>
+      <c r="K50" s="42">
+        <f>'ESWE KPIs'!C38</f>
+        <v/>
+      </c>
+      <c r="L50" s="42">
+        <f>'ESWE KPIs'!D38</f>
+        <v/>
+      </c>
+      <c r="M50" s="42">
+        <f>'ESWE KPIs'!E38</f>
+        <v/>
+      </c>
+      <c r="N50" s="42">
+        <f>'ESWE KPIs'!F38</f>
+        <v/>
+      </c>
+      <c r="O50" s="43">
+        <f>'ESWE KPIs'!G38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="J51" s="26" t="inlineStr">
+        <is>
+          <t>Wassernetz (Mio. m³)</t>
+        </is>
+      </c>
+      <c r="K51" s="27">
+        <f>'ESWE KPIs'!C39</f>
+        <v/>
+      </c>
+      <c r="L51" s="27">
+        <f>'ESWE KPIs'!D39</f>
+        <v/>
+      </c>
+      <c r="M51" s="27">
+        <f>'ESWE KPIs'!E39</f>
+        <v/>
+      </c>
+      <c r="N51" s="27">
+        <f>'ESWE KPIs'!F39</f>
+        <v/>
+      </c>
+      <c r="O51" s="28">
+        <f>'ESWE KPIs'!G39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="J53" s="14" t="inlineStr">
+        <is>
+          <t>Diese Blöcke sind reine Quellbereiche für Diagramme: jede Zelle verweist grün auf die Übersicht bzw. auf ein Detailblatt, es werden keine Werte doppelt erfasst. Beim Einfügen eines Diagramms genügt es, den jeweiligen Block inklusive Kopfzeile zu markieren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54"/>
+    <row r="55"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="J53:O55"/>
     <mergeCell ref="B45:G46"/>
     <mergeCell ref="B42:G43"/>
   </mergeCells>
@@ -2129,16 +3086,16 @@
   </cols>
   <sheetData>
     <row r="2" ht="21" customHeight="1">
-      <c r="B2" s="28" t="inlineStr">
+      <c r="B2" s="44" t="inlineStr">
         <is>
           <t>ESWE Versorgungs AG – Bilanz zum 31. Dezember 2021–2025</t>
         </is>
       </c>
-      <c r="C2" s="28" t="n"/>
-      <c r="D2" s="28" t="n"/>
-      <c r="E2" s="28" t="n"/>
-      <c r="F2" s="28" t="n"/>
-      <c r="G2" s="28" t="n"/>
+      <c r="C2" s="44" t="n"/>
+      <c r="D2" s="44" t="n"/>
+      <c r="E2" s="44" t="n"/>
+      <c r="F2" s="44" t="n"/>
+      <c r="G2" s="44" t="n"/>
     </row>
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
@@ -2174,188 +3131,188 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="45" t="inlineStr">
         <is>
           <t>A. Anlagevermögen (1)</t>
         </is>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="46">
         <f>SUM(C7:C9)</f>
         <v/>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="46">
         <f>SUM(D7:D9)</f>
         <v/>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="46">
         <f>SUM(E7:E9)</f>
         <v/>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="46">
         <f>SUM(F7:F9)</f>
         <v/>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="46">
         <f>SUM(G7:G9)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="47" t="inlineStr">
         <is>
           <t>I. Immaterielle Vermögensgegenstände</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n">
+      <c r="C7" s="48" t="n">
         <v>1.044</v>
       </c>
-      <c r="D7" s="32" t="n">
+      <c r="D7" s="48" t="n">
         <v>0.8110000000000001</v>
       </c>
-      <c r="E7" s="32" t="n">
+      <c r="E7" s="48" t="n">
         <v>0.658</v>
       </c>
-      <c r="F7" s="32" t="n">
+      <c r="F7" s="48" t="n">
         <v>0.877</v>
       </c>
-      <c r="G7" s="32" t="n">
+      <c r="G7" s="48" t="n">
         <v>0.764</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="47" t="inlineStr">
         <is>
           <t>II. Sachanlagen</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n">
+      <c r="C8" s="48" t="n">
         <v>174.058</v>
       </c>
-      <c r="D8" s="32" t="n">
+      <c r="D8" s="48" t="n">
         <v>189.12</v>
       </c>
-      <c r="E8" s="32" t="n">
+      <c r="E8" s="48" t="n">
         <v>197.803</v>
       </c>
-      <c r="F8" s="32" t="n">
+      <c r="F8" s="48" t="n">
         <v>209.24</v>
       </c>
-      <c r="G8" s="32" t="n">
+      <c r="G8" s="48" t="n">
         <v>223.938</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" s="47" t="inlineStr">
         <is>
           <t>III. Finanzanlagen</t>
         </is>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="48" t="n">
         <v>148.234</v>
       </c>
-      <c r="D9" s="32" t="n">
+      <c r="D9" s="48" t="n">
         <v>170.186</v>
       </c>
-      <c r="E9" s="32" t="n">
+      <c r="E9" s="48" t="n">
         <v>171.96</v>
       </c>
-      <c r="F9" s="32" t="n">
+      <c r="F9" s="48" t="n">
         <v>165.19</v>
       </c>
-      <c r="G9" s="32" t="n">
+      <c r="G9" s="48" t="n">
         <v>170.025</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" s="45" t="inlineStr">
         <is>
           <t>B. Umlaufvermögen</t>
         </is>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="46">
         <f>SUM(C12:C14)</f>
         <v/>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="46">
         <f>SUM(D12:D14)</f>
         <v/>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="46">
         <f>SUM(E12:E14)</f>
         <v/>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="46">
         <f>SUM(F12:F14)</f>
         <v/>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="46">
         <f>SUM(G12:G14)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="31" t="inlineStr">
+      <c r="B12" s="47" t="inlineStr">
         <is>
           <t>I. Vorräte (2)</t>
         </is>
       </c>
-      <c r="C12" s="32" t="n">
+      <c r="C12" s="48" t="n">
         <v>7.162</v>
       </c>
-      <c r="D12" s="32" t="n">
+      <c r="D12" s="48" t="n">
         <v>8.157999999999999</v>
       </c>
-      <c r="E12" s="32" t="n">
+      <c r="E12" s="48" t="n">
         <v>15.439</v>
       </c>
-      <c r="F12" s="32" t="n">
+      <c r="F12" s="48" t="n">
         <v>18.356</v>
       </c>
-      <c r="G12" s="32" t="n">
+      <c r="G12" s="48" t="n">
         <v>17.857</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" s="47" t="inlineStr">
         <is>
           <t>II. Forderungen und sonstige Vermögensgegenstände (3)</t>
         </is>
       </c>
-      <c r="C13" s="32" t="n">
+      <c r="C13" s="48" t="n">
         <v>48.391</v>
       </c>
-      <c r="D13" s="32" t="n">
+      <c r="D13" s="48" t="n">
         <v>17.853</v>
       </c>
-      <c r="E13" s="32" t="n">
+      <c r="E13" s="48" t="n">
         <v>46.747</v>
       </c>
-      <c r="F13" s="32" t="n">
+      <c r="F13" s="48" t="n">
         <v>43.316</v>
       </c>
-      <c r="G13" s="32" t="n">
+      <c r="G13" s="48" t="n">
         <v>63.663</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="31" t="inlineStr">
+      <c r="B14" s="47" t="inlineStr">
         <is>
           <t>III. Kassenbestand und Guthaben bei Kreditinstituten</t>
         </is>
       </c>
-      <c r="C14" s="32" t="n">
+      <c r="C14" s="48" t="n">
         <v>3.616</v>
       </c>
-      <c r="D14" s="32" t="n">
+      <c r="D14" s="48" t="n">
         <v>30.611</v>
       </c>
-      <c r="E14" s="32" t="n">
+      <c r="E14" s="48" t="n">
         <v>44.992</v>
       </c>
-      <c r="F14" s="32" t="n">
+      <c r="F14" s="48" t="n">
         <v>21.543</v>
       </c>
-      <c r="G14" s="32" t="n">
+      <c r="G14" s="48" t="n">
         <v>2.517</v>
       </c>
     </row>
@@ -2365,45 +3322,45 @@
           <t>C. Rechnungsabgrenzungsposten</t>
         </is>
       </c>
-      <c r="C16" s="33" t="n">
+      <c r="C16" s="49" t="n">
         <v>2.468</v>
       </c>
-      <c r="D16" s="33" t="n">
+      <c r="D16" s="49" t="n">
         <v>3.089</v>
       </c>
-      <c r="E16" s="33" t="n">
+      <c r="E16" s="49" t="n">
         <v>3.588</v>
       </c>
-      <c r="F16" s="33" t="n">
+      <c r="F16" s="49" t="n">
         <v>0.581</v>
       </c>
-      <c r="G16" s="33" t="n">
+      <c r="G16" s="49" t="n">
         <v>0.819</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>Bilanzsumme Aktiva</t>
         </is>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="40">
         <f>C6+C11+C16</f>
         <v/>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="40">
         <f>D6+D11+D16</f>
         <v/>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="40">
         <f>E6+E11+E16</f>
         <v/>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="40">
         <f>F6+F11+F16</f>
         <v/>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="40">
         <f>G6+G11+G16</f>
         <v/>
       </c>
@@ -2416,117 +3373,117 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="29" t="inlineStr">
+      <c r="B20" s="45" t="inlineStr">
         <is>
           <t>A. Eigenkapital (4)</t>
         </is>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="46">
         <f>SUM(C21:C24)</f>
         <v/>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="46">
         <f>SUM(D21:D24)</f>
         <v/>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="46">
         <f>SUM(E21:E24)</f>
         <v/>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="46">
         <f>SUM(F21:F24)</f>
         <v/>
       </c>
-      <c r="G20" s="30">
+      <c r="G20" s="46">
         <f>SUM(G21:G24)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="31" t="inlineStr">
+      <c r="B21" s="47" t="inlineStr">
         <is>
           <t>I. Gezeichnetes Kapital</t>
         </is>
       </c>
-      <c r="C21" s="32" t="n">
+      <c r="C21" s="48" t="n">
         <v>66.01300000000001</v>
       </c>
-      <c r="D21" s="32" t="n">
+      <c r="D21" s="48" t="n">
         <v>66.01300000000001</v>
       </c>
-      <c r="E21" s="32" t="n">
+      <c r="E21" s="48" t="n">
         <v>66.01300000000001</v>
       </c>
-      <c r="F21" s="32" t="n">
+      <c r="F21" s="48" t="n">
         <v>66.01300000000001</v>
       </c>
-      <c r="G21" s="32" t="n">
+      <c r="G21" s="48" t="n">
         <v>66.01300000000001</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="31" t="inlineStr">
+      <c r="B22" s="47" t="inlineStr">
         <is>
           <t>II. Kapitalrücklage</t>
         </is>
       </c>
-      <c r="C22" s="32" t="n">
+      <c r="C22" s="48" t="n">
         <v>25.426</v>
       </c>
-      <c r="D22" s="32" t="n">
+      <c r="D22" s="48" t="n">
         <v>25.426</v>
       </c>
-      <c r="E22" s="32" t="n">
+      <c r="E22" s="48" t="n">
         <v>25.426</v>
       </c>
-      <c r="F22" s="32" t="n">
+      <c r="F22" s="48" t="n">
         <v>25.426</v>
       </c>
-      <c r="G22" s="32" t="n">
+      <c r="G22" s="48" t="n">
         <v>35.426</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="31" t="inlineStr">
+      <c r="B23" s="47" t="inlineStr">
         <is>
           <t>III. Gewinnrücklagen</t>
         </is>
       </c>
-      <c r="C23" s="32" t="n">
+      <c r="C23" s="48" t="n">
         <v>25.131</v>
       </c>
-      <c r="D23" s="32" t="n">
+      <c r="D23" s="48" t="n">
         <v>25.131</v>
       </c>
-      <c r="E23" s="32" t="n">
+      <c r="E23" s="48" t="n">
         <v>35.131</v>
       </c>
-      <c r="F23" s="32" t="n">
+      <c r="F23" s="48" t="n">
         <v>35.131</v>
       </c>
-      <c r="G23" s="32" t="n">
+      <c r="G23" s="48" t="n">
         <v>35.131</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="31" t="inlineStr">
+      <c r="B24" s="47" t="inlineStr">
         <is>
           <t>IV. Bilanzgewinn</t>
         </is>
       </c>
-      <c r="C24" s="32" t="n">
+      <c r="C24" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="32" t="n">
+      <c r="D24" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="32" t="n">
+      <c r="E24" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="32" t="n">
+      <c r="F24" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="32" t="n">
+      <c r="G24" s="48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2536,19 +3493,19 @@
           <t>B. Empfangene Ertragszuschüsse</t>
         </is>
       </c>
-      <c r="C26" s="33" t="n">
+      <c r="C26" s="49" t="n">
         <v>28.577</v>
       </c>
-      <c r="D26" s="33" t="n">
+      <c r="D26" s="49" t="n">
         <v>28.9</v>
       </c>
-      <c r="E26" s="33" t="n">
+      <c r="E26" s="49" t="n">
         <v>28.009</v>
       </c>
-      <c r="F26" s="33" t="n">
+      <c r="F26" s="49" t="n">
         <v>27.685</v>
       </c>
-      <c r="G26" s="33" t="n">
+      <c r="G26" s="49" t="n">
         <v>29.619</v>
       </c>
     </row>
@@ -2558,19 +3515,19 @@
           <t>C. Rückstellungen (5)</t>
         </is>
       </c>
-      <c r="C27" s="33" t="n">
+      <c r="C27" s="49" t="n">
         <v>95.422</v>
       </c>
-      <c r="D27" s="33" t="n">
+      <c r="D27" s="49" t="n">
         <v>90.794</v>
       </c>
-      <c r="E27" s="33" t="n">
+      <c r="E27" s="49" t="n">
         <v>111.63</v>
       </c>
-      <c r="F27" s="33" t="n">
+      <c r="F27" s="49" t="n">
         <v>91.974</v>
       </c>
-      <c r="G27" s="33" t="n">
+      <c r="G27" s="49" t="n">
         <v>92.117</v>
       </c>
     </row>
@@ -2580,41 +3537,41 @@
           <t>D. Verbindlichkeiten (6)</t>
         </is>
       </c>
-      <c r="C28" s="33" t="n">
+      <c r="C28" s="49" t="n">
         <v>144.38</v>
       </c>
-      <c r="D28" s="33" t="n">
+      <c r="D28" s="49" t="n">
         <v>183.564</v>
       </c>
-      <c r="E28" s="33" t="n">
+      <c r="E28" s="49" t="n">
         <v>214.912</v>
       </c>
-      <c r="F28" s="33" t="n">
+      <c r="F28" s="49" t="n">
         <v>212.874</v>
       </c>
-      <c r="G28" s="33" t="n">
+      <c r="G28" s="49" t="n">
         <v>221.277</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="31" t="inlineStr">
+      <c r="B29" s="47" t="inlineStr">
         <is>
           <t>davon gegenüber Kreditinstituten</t>
         </is>
       </c>
-      <c r="C29" s="32" t="n">
+      <c r="C29" s="48" t="n">
         <v>79</v>
       </c>
-      <c r="D29" s="32" t="n">
+      <c r="D29" s="48" t="n">
         <v>98.65900000000001</v>
       </c>
-      <c r="E29" s="32" t="n">
+      <c r="E29" s="48" t="n">
         <v>110.748</v>
       </c>
-      <c r="F29" s="32" t="n">
+      <c r="F29" s="48" t="n">
         <v>119.911</v>
       </c>
-      <c r="G29" s="32" t="n">
+      <c r="G29" s="48" t="n">
         <v>124.179</v>
       </c>
     </row>
@@ -2624,45 +3581,45 @@
           <t>E. Rechnungsabgrenzungsposten</t>
         </is>
       </c>
-      <c r="C30" s="33" t="n">
+      <c r="C30" s="49" t="n">
         <v>0.024</v>
       </c>
-      <c r="D30" s="33" t="n">
+      <c r="D30" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="33" t="n">
+      <c r="E30" s="49" t="n">
         <v>0.066</v>
       </c>
-      <c r="F30" s="33" t="n">
+      <c r="F30" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="33" t="n">
+      <c r="G30" s="49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B31" s="39" t="inlineStr">
         <is>
           <t>Bilanzsumme Passiva</t>
         </is>
       </c>
-      <c r="C31" s="26">
+      <c r="C31" s="40">
         <f>C20+C26+C27+C28+C30</f>
         <v/>
       </c>
-      <c r="D31" s="26">
+      <c r="D31" s="40">
         <f>D20+D26+D27+D28+D30</f>
         <v/>
       </c>
-      <c r="E31" s="26">
+      <c r="E31" s="40">
         <f>E20+E26+E27+E28+E30</f>
         <v/>
       </c>
-      <c r="F31" s="26">
+      <c r="F31" s="40">
         <f>F20+F26+F27+F28+F30</f>
         <v/>
       </c>
-      <c r="G31" s="26">
+      <c r="G31" s="40">
         <f>G20+G26+G27+G28+G30</f>
         <v/>
       </c>
@@ -2673,23 +3630,23 @@
           <t>Kontrolle: Bilanzsumme Aktiva ./. Passiva (muss 0 sein)</t>
         </is>
       </c>
-      <c r="C33" s="34">
+      <c r="C33" s="50">
         <f>ROUND(C17-C31,6)</f>
         <v/>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="50">
         <f>ROUND(D17-D31,6)</f>
         <v/>
       </c>
-      <c r="E33" s="34">
+      <c r="E33" s="50">
         <f>ROUND(E17-E31,6)</f>
         <v/>
       </c>
-      <c r="F33" s="34">
+      <c r="F33" s="50">
         <f>ROUND(F17-F31,6)</f>
         <v/>
       </c>
-      <c r="G33" s="34">
+      <c r="G33" s="50">
         <f>ROUND(G17-G31,6)</f>
         <v/>
       </c>
@@ -2730,16 +3687,16 @@
   </cols>
   <sheetData>
     <row r="2" ht="21" customHeight="1">
-      <c r="B2" s="28" t="inlineStr">
+      <c r="B2" s="44" t="inlineStr">
         <is>
           <t>ESWE Versorgungs AG – Gewinn- und Verlustrechnung 2021–2025</t>
         </is>
       </c>
-      <c r="C2" s="28" t="n"/>
-      <c r="D2" s="28" t="n"/>
-      <c r="E2" s="28" t="n"/>
-      <c r="F2" s="28" t="n"/>
-      <c r="G2" s="28" t="n"/>
+      <c r="C2" s="44" t="n"/>
+      <c r="D2" s="44" t="n"/>
+      <c r="E2" s="44" t="n"/>
+      <c r="F2" s="44" t="n"/>
+      <c r="G2" s="44" t="n"/>
     </row>
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
@@ -2773,19 +3730,19 @@
           <t>1. Umsatzerlöse (10)</t>
         </is>
       </c>
-      <c r="C5" s="33" t="n">
+      <c r="C5" s="49" t="n">
         <v>426.532</v>
       </c>
-      <c r="D5" s="33" t="n">
+      <c r="D5" s="49" t="n">
         <v>475.683</v>
       </c>
-      <c r="E5" s="33" t="n">
+      <c r="E5" s="49" t="n">
         <v>634.062</v>
       </c>
-      <c r="F5" s="33" t="n">
+      <c r="F5" s="49" t="n">
         <v>534.653</v>
       </c>
-      <c r="G5" s="33" t="n">
+      <c r="G5" s="49" t="n">
         <v>473.77</v>
       </c>
     </row>
@@ -2795,19 +3752,19 @@
           <t>2. Veränderung des Bestands an unfertigen Leistungen</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n">
+      <c r="C6" s="48" t="n">
         <v>-0.332</v>
       </c>
-      <c r="D6" s="32" t="n">
+      <c r="D6" s="48" t="n">
         <v>0.86</v>
       </c>
-      <c r="E6" s="32" t="n">
+      <c r="E6" s="48" t="n">
         <v>0.8110000000000001</v>
       </c>
-      <c r="F6" s="32" t="n">
+      <c r="F6" s="48" t="n">
         <v>0.06900000000000001</v>
       </c>
-      <c r="G6" s="32" t="n">
+      <c r="G6" s="48" t="n">
         <v>-0.545</v>
       </c>
     </row>
@@ -2817,19 +3774,19 @@
           <t>3. Andere aktivierte Eigenleistungen (11)</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n">
+      <c r="C7" s="48" t="n">
         <v>3.399</v>
       </c>
-      <c r="D7" s="32" t="n">
+      <c r="D7" s="48" t="n">
         <v>3.309</v>
       </c>
-      <c r="E7" s="32" t="n">
+      <c r="E7" s="48" t="n">
         <v>1.873</v>
       </c>
-      <c r="F7" s="32" t="n">
+      <c r="F7" s="48" t="n">
         <v>2.674</v>
       </c>
-      <c r="G7" s="32" t="n">
+      <c r="G7" s="48" t="n">
         <v>2.992</v>
       </c>
     </row>
@@ -2839,19 +3796,19 @@
           <t>4. Sonstige betriebliche Erträge (12)</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n">
+      <c r="C8" s="48" t="n">
         <v>2.486</v>
       </c>
-      <c r="D8" s="32" t="n">
+      <c r="D8" s="48" t="n">
         <v>5.989</v>
       </c>
-      <c r="E8" s="32" t="n">
+      <c r="E8" s="48" t="n">
         <v>6.383</v>
       </c>
-      <c r="F8" s="32" t="n">
+      <c r="F8" s="48" t="n">
         <v>30.279</v>
       </c>
-      <c r="G8" s="32" t="n">
+      <c r="G8" s="48" t="n">
         <v>9.708</v>
       </c>
     </row>
@@ -2861,19 +3818,19 @@
           <t>5. Materialaufwand (13)</t>
         </is>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="48" t="n">
         <v>311.386</v>
       </c>
-      <c r="D9" s="32" t="n">
+      <c r="D9" s="48" t="n">
         <v>356.302</v>
       </c>
-      <c r="E9" s="32" t="n">
+      <c r="E9" s="48" t="n">
         <v>483.927</v>
       </c>
-      <c r="F9" s="32" t="n">
+      <c r="F9" s="48" t="n">
         <v>387.16</v>
       </c>
-      <c r="G9" s="32" t="n">
+      <c r="G9" s="48" t="n">
         <v>341.791</v>
       </c>
     </row>
@@ -2883,19 +3840,19 @@
           <t>6. Personalaufwand (14)</t>
         </is>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C10" s="48" t="n">
         <v>50.803</v>
       </c>
-      <c r="D10" s="32" t="n">
+      <c r="D10" s="48" t="n">
         <v>52.128</v>
       </c>
-      <c r="E10" s="32" t="n">
+      <c r="E10" s="48" t="n">
         <v>52.026</v>
       </c>
-      <c r="F10" s="32" t="n">
+      <c r="F10" s="48" t="n">
         <v>55.317</v>
       </c>
-      <c r="G10" s="32" t="n">
+      <c r="G10" s="48" t="n">
         <v>60.837</v>
       </c>
     </row>
@@ -2905,19 +3862,19 @@
           <t>7. Abschreibungen (15)</t>
         </is>
       </c>
-      <c r="C11" s="32" t="n">
+      <c r="C11" s="48" t="n">
         <v>14.18</v>
       </c>
-      <c r="D11" s="32" t="n">
+      <c r="D11" s="48" t="n">
         <v>14.545</v>
       </c>
-      <c r="E11" s="32" t="n">
+      <c r="E11" s="48" t="n">
         <v>14.57</v>
       </c>
-      <c r="F11" s="32" t="n">
+      <c r="F11" s="48" t="n">
         <v>15.673</v>
       </c>
-      <c r="G11" s="32" t="n">
+      <c r="G11" s="48" t="n">
         <v>16.427</v>
       </c>
     </row>
@@ -2927,45 +3884,45 @@
           <t>8. Sonstige betriebliche Aufwendungen (16)</t>
         </is>
       </c>
-      <c r="C12" s="32" t="n">
+      <c r="C12" s="48" t="n">
         <v>35.338</v>
       </c>
-      <c r="D12" s="32" t="n">
+      <c r="D12" s="48" t="n">
         <v>26.581</v>
       </c>
-      <c r="E12" s="32" t="n">
+      <c r="E12" s="48" t="n">
         <v>49.684</v>
       </c>
-      <c r="F12" s="32" t="n">
+      <c r="F12" s="48" t="n">
         <v>36.261</v>
       </c>
-      <c r="G12" s="32" t="n">
+      <c r="G12" s="48" t="n">
         <v>38.141</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="39" t="inlineStr">
         <is>
           <t>9. Betriebliches Ergebnis</t>
         </is>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="40">
         <f>SUM(C5:C8)-SUM(C9:C12)</f>
         <v/>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="40">
         <f>SUM(D5:D8)-SUM(D9:D12)</f>
         <v/>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="40">
         <f>SUM(E5:E8)-SUM(E9:E12)</f>
         <v/>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="40">
         <f>SUM(F5:F8)-SUM(F9:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="40">
         <f>SUM(G5:G8)-SUM(G9:G12)</f>
         <v/>
       </c>
@@ -2976,19 +3933,19 @@
           <t>10. Beteiligungsergebnis (17)</t>
         </is>
       </c>
-      <c r="C15" s="32" t="n">
+      <c r="C15" s="48" t="n">
         <v>24.466</v>
       </c>
-      <c r="D15" s="32" t="n">
+      <c r="D15" s="48" t="n">
         <v>17.558</v>
       </c>
-      <c r="E15" s="32" t="n">
+      <c r="E15" s="48" t="n">
         <v>30.534</v>
       </c>
-      <c r="F15" s="32" t="n">
+      <c r="F15" s="48" t="n">
         <v>17.765</v>
       </c>
-      <c r="G15" s="32" t="n">
+      <c r="G15" s="48" t="n">
         <v>25.06</v>
       </c>
     </row>
@@ -2998,19 +3955,19 @@
           <t>11. Abschreibungen auf Finanzanlagen (18)</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n">
+      <c r="C16" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="32" t="n">
+      <c r="D16" s="48" t="n">
         <v>2.037</v>
       </c>
-      <c r="E16" s="32" t="n">
+      <c r="E16" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="32" t="n">
+      <c r="F16" s="48" t="n">
         <v>8.965</v>
       </c>
-      <c r="G16" s="32" t="n">
+      <c r="G16" s="48" t="n">
         <v>0.388</v>
       </c>
     </row>
@@ -3020,45 +3977,45 @@
           <t>12. Zinsergebnis (19)</t>
         </is>
       </c>
-      <c r="C17" s="32" t="n">
+      <c r="C17" s="48" t="n">
         <v>-0.767</v>
       </c>
-      <c r="D17" s="32" t="n">
+      <c r="D17" s="48" t="n">
         <v>-0.049</v>
       </c>
-      <c r="E17" s="32" t="n">
+      <c r="E17" s="48" t="n">
         <v>1.281</v>
       </c>
-      <c r="F17" s="32" t="n">
+      <c r="F17" s="48" t="n">
         <v>2.218</v>
       </c>
-      <c r="G17" s="32" t="n">
+      <c r="G17" s="48" t="n">
         <v>-0.751</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>13. Ergebnis vor Steuern</t>
         </is>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="40">
         <f>C13+C15-C16+C17</f>
         <v/>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="40">
         <f>D13+D15-D16+D17</f>
         <v/>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="40">
         <f>E13+E15-E16+E17</f>
         <v/>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="40">
         <f>F13+F15-F16+F17</f>
         <v/>
       </c>
-      <c r="G18" s="26">
+      <c r="G18" s="40">
         <f>G13+G15-G16+G17</f>
         <v/>
       </c>
@@ -3069,45 +4026,45 @@
           <t>14. Steuern vom Einkommen und vom Ertrag (20)</t>
         </is>
       </c>
-      <c r="C20" s="32" t="n">
+      <c r="C20" s="48" t="n">
         <v>3.034</v>
       </c>
-      <c r="D20" s="32" t="n">
+      <c r="D20" s="48" t="n">
         <v>3.214</v>
       </c>
-      <c r="E20" s="32" t="n">
+      <c r="E20" s="48" t="n">
         <v>3.939</v>
       </c>
-      <c r="F20" s="32" t="n">
+      <c r="F20" s="48" t="n">
         <v>5.544</v>
       </c>
-      <c r="G20" s="32" t="n">
+      <c r="G20" s="48" t="n">
         <v>3.494</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="25" t="inlineStr">
+      <c r="B21" s="39" t="inlineStr">
         <is>
           <t>15. Ergebnis nach Steuern</t>
         </is>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="40">
         <f>C18-C20</f>
         <v/>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="40">
         <f>D18-D20</f>
         <v/>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="40">
         <f>E18-E20</f>
         <v/>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="40">
         <f>F18-F20</f>
         <v/>
       </c>
-      <c r="G21" s="26">
+      <c r="G21" s="40">
         <f>G18-G20</f>
         <v/>
       </c>
@@ -3118,45 +4075,45 @@
           <t>16. Sonstige Steuern (21)</t>
         </is>
       </c>
-      <c r="C23" s="32" t="n">
+      <c r="C23" s="48" t="n">
         <v>0.3</v>
       </c>
-      <c r="D23" s="32" t="n">
+      <c r="D23" s="48" t="n">
         <v>0.308</v>
       </c>
-      <c r="E23" s="32" t="n">
+      <c r="E23" s="48" t="n">
         <v>0.237</v>
       </c>
-      <c r="F23" s="32" t="n">
+      <c r="F23" s="48" t="n">
         <v>0.44</v>
       </c>
-      <c r="G23" s="32" t="n">
+      <c r="G23" s="48" t="n">
         <v>0.271</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B24" s="39" t="inlineStr">
         <is>
           <t>17. Unternehmensergebnis / Jahresüberschuss</t>
         </is>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="40">
         <f>C21-C23</f>
         <v/>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="40">
         <f>D21-D23</f>
         <v/>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="40">
         <f>E21-E23</f>
         <v/>
       </c>
-      <c r="F24" s="26">
+      <c r="F24" s="40">
         <f>F21-F23</f>
         <v/>
       </c>
-      <c r="G24" s="26">
+      <c r="G24" s="40">
         <f>G21-G23</f>
         <v/>
       </c>
@@ -3167,19 +4124,19 @@
           <t>18. Einstellung in die anderen Gewinnrücklagen (22)</t>
         </is>
       </c>
-      <c r="C26" s="32" t="n">
+      <c r="C26" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="32" t="n">
+      <c r="D26" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="32" t="n">
+      <c r="E26" s="48" t="n">
         <v>10</v>
       </c>
-      <c r="F26" s="32" t="n">
+      <c r="F26" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="32" t="n">
+      <c r="G26" s="48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3189,19 +4146,19 @@
           <t>19. Aufwendungen für Ausgleichszahlung</t>
         </is>
       </c>
-      <c r="C27" s="32" t="n">
+      <c r="C27" s="48" t="n">
         <v>16.295</v>
       </c>
-      <c r="D27" s="32" t="n">
+      <c r="D27" s="48" t="n">
         <v>17.312</v>
       </c>
-      <c r="E27" s="32" t="n">
+      <c r="E27" s="48" t="n">
         <v>21.109</v>
       </c>
-      <c r="F27" s="32" t="n">
+      <c r="F27" s="48" t="n">
         <v>29.779</v>
       </c>
-      <c r="G27" s="32" t="n">
+      <c r="G27" s="48" t="n">
         <v>18.768</v>
       </c>
     </row>
@@ -3211,45 +4168,45 @@
           <t>20. Aufgrund eines Ergebnisabführungsvertrags abgeführter Gewinn</t>
         </is>
       </c>
-      <c r="C28" s="32" t="n">
+      <c r="C28" s="48" t="n">
         <v>24.448</v>
       </c>
-      <c r="D28" s="32" t="n">
+      <c r="D28" s="48" t="n">
         <v>30.923</v>
       </c>
-      <c r="E28" s="32" t="n">
+      <c r="E28" s="48" t="n">
         <v>39.452</v>
       </c>
-      <c r="F28" s="32" t="n">
+      <c r="F28" s="48" t="n">
         <v>48.519</v>
       </c>
-      <c r="G28" s="32" t="n">
+      <c r="G28" s="48" t="n">
         <v>30.117</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B29" s="39" t="inlineStr">
         <is>
           <t>21. Bilanzgewinn</t>
         </is>
       </c>
-      <c r="C29" s="26">
+      <c r="C29" s="40">
         <f>C24-SUM(C26:C28)</f>
         <v/>
       </c>
-      <c r="D29" s="26">
+      <c r="D29" s="40">
         <f>D24-SUM(D26:D28)</f>
         <v/>
       </c>
-      <c r="E29" s="26">
+      <c r="E29" s="40">
         <f>E24-SUM(E26:E28)</f>
         <v/>
       </c>
-      <c r="F29" s="26">
+      <c r="F29" s="40">
         <f>F24-SUM(F26:F28)</f>
         <v/>
       </c>
-      <c r="G29" s="26">
+      <c r="G29" s="40">
         <f>G24-SUM(G26:G28)</f>
         <v/>
       </c>
@@ -3260,23 +4217,23 @@
           <t>Kontrolle: Bilanzgewinn GuV ./. Bilanzgewinn Bilanz (muss 0 sein)</t>
         </is>
       </c>
-      <c r="C31" s="34">
+      <c r="C31" s="50">
         <f>ROUND(C29-'ESWE Bilanz'!C24,6)</f>
         <v/>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="50">
         <f>ROUND(D29-'ESWE Bilanz'!D24,6)</f>
         <v/>
       </c>
-      <c r="E31" s="34">
+      <c r="E31" s="50">
         <f>ROUND(E29-'ESWE Bilanz'!E24,6)</f>
         <v/>
       </c>
-      <c r="F31" s="34">
+      <c r="F31" s="50">
         <f>ROUND(F29-'ESWE Bilanz'!F24,6)</f>
         <v/>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="50">
         <f>ROUND(G29-'ESWE Bilanz'!G24,6)</f>
         <v/>
       </c>
@@ -3317,16 +4274,16 @@
   </cols>
   <sheetData>
     <row r="2" ht="21" customHeight="1">
-      <c r="B2" s="28" t="inlineStr">
+      <c r="B2" s="44" t="inlineStr">
         <is>
           <t>ESWE Versorgungs AG – Kapitalflussrechnung nach DRS 21 2021–2025</t>
         </is>
       </c>
-      <c r="C2" s="28" t="n"/>
-      <c r="D2" s="28" t="n"/>
-      <c r="E2" s="28" t="n"/>
-      <c r="F2" s="28" t="n"/>
-      <c r="G2" s="28" t="n"/>
+      <c r="C2" s="44" t="n"/>
+      <c r="D2" s="44" t="n"/>
+      <c r="E2" s="44" t="n"/>
+      <c r="F2" s="44" t="n"/>
+      <c r="G2" s="44" t="n"/>
     </row>
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
@@ -3360,19 +4317,19 @@
           <t>(+) Cashflow aus laufender Geschäftstätigkeit</t>
         </is>
       </c>
-      <c r="C5" s="33" t="n">
+      <c r="C5" s="49" t="n">
         <v>49</v>
       </c>
-      <c r="D5" s="33" t="n">
+      <c r="D5" s="49" t="n">
         <v>78</v>
       </c>
-      <c r="E5" s="33" t="n">
+      <c r="E5" s="49" t="n">
         <v>47.3</v>
       </c>
-      <c r="F5" s="33" t="n">
+      <c r="F5" s="49" t="n">
         <v>68.2</v>
       </c>
-      <c r="G5" s="33" t="n">
+      <c r="G5" s="49" t="n">
         <v>42.7</v>
       </c>
     </row>
@@ -3382,19 +4339,19 @@
           <t>(+) Cashflow aus der Investitionstätigkeit</t>
         </is>
       </c>
-      <c r="C6" s="33" t="n">
+      <c r="C6" s="49" t="n">
         <v>-19.5</v>
       </c>
-      <c r="D6" s="33" t="n">
+      <c r="D6" s="49" t="n">
         <v>-34</v>
       </c>
-      <c r="E6" s="33" t="n">
+      <c r="E6" s="49" t="n">
         <v>8.9</v>
       </c>
-      <c r="F6" s="33" t="n">
+      <c r="F6" s="49" t="n">
         <v>-5</v>
       </c>
-      <c r="G6" s="33" t="n">
+      <c r="G6" s="49" t="n">
         <v>-8.300000000000001</v>
       </c>
     </row>
@@ -3404,45 +4361,45 @@
           <t>(+) Cashflow aus der Finanzierungstätigkeit</t>
         </is>
       </c>
-      <c r="C7" s="33" t="n">
+      <c r="C7" s="49" t="n">
         <v>-28.9</v>
       </c>
-      <c r="D7" s="33" t="n">
+      <c r="D7" s="49" t="n">
         <v>-17</v>
       </c>
-      <c r="E7" s="33" t="n">
+      <c r="E7" s="49" t="n">
         <v>-41.8</v>
       </c>
-      <c r="F7" s="33" t="n">
+      <c r="F7" s="49" t="n">
         <v>-86.7</v>
       </c>
-      <c r="G7" s="33" t="n">
+      <c r="G7" s="49" t="n">
         <v>-53.4</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="45" t="inlineStr">
         <is>
           <t>(=) Zahlungswirksame Veränderung des Finanzmittelfonds</t>
         </is>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="46">
         <f>SUM(C5:C7)</f>
         <v/>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="46">
         <f>SUM(D5:D7)</f>
         <v/>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="46">
         <f>SUM(E5:E7)</f>
         <v/>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="46">
         <f>SUM(F5:F7)</f>
         <v/>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="46">
         <f>SUM(G5:G7)</f>
         <v/>
       </c>
@@ -3453,45 +4410,45 @@
           <t>(+) Finanzmittelfonds am Anfang der Periode</t>
         </is>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C10" s="48" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="32" t="n">
+      <c r="D10" s="48" t="n">
         <v>3.6</v>
       </c>
-      <c r="E10" s="32" t="n">
+      <c r="E10" s="48" t="n">
         <v>30.6</v>
       </c>
-      <c r="F10" s="32" t="n">
+      <c r="F10" s="48" t="n">
         <v>45</v>
       </c>
-      <c r="G10" s="32" t="n">
+      <c r="G10" s="48" t="n">
         <v>21.5</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="39" t="inlineStr">
         <is>
           <t>Finanzmittelfonds am Ende der Periode</t>
         </is>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="40">
         <f>C10+C9</f>
         <v/>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="40">
         <f>D10+D9</f>
         <v/>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="40">
         <f>E10+E9</f>
         <v/>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="40">
         <f>F10+F9</f>
         <v/>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="40">
         <f>G10+G9</f>
         <v/>
       </c>
@@ -3502,19 +4459,19 @@
           <t>nachrichtlich: veröffentlichter Endbestand lt. Lagebericht</t>
         </is>
       </c>
-      <c r="C13" s="32" t="n">
+      <c r="C13" s="48" t="n">
         <v>3.6</v>
       </c>
-      <c r="D13" s="32" t="n">
+      <c r="D13" s="48" t="n">
         <v>30.6</v>
       </c>
-      <c r="E13" s="32" t="n">
+      <c r="E13" s="48" t="n">
         <v>45</v>
       </c>
-      <c r="F13" s="32" t="n">
+      <c r="F13" s="48" t="n">
         <v>21.5</v>
       </c>
-      <c r="G13" s="32" t="n">
+      <c r="G13" s="48" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -3524,23 +4481,23 @@
           <t>Kontrolle: berechneter ./. veröffentlichter Endbestand (muss 0 sein)</t>
         </is>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="50">
         <f>ROUND(C11-C13,1)</f>
         <v/>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="50">
         <f>ROUND(D11-D13,1)</f>
         <v/>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="50">
         <f>ROUND(E11-E13,1)</f>
         <v/>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="50">
         <f>ROUND(F11-F13,1)</f>
         <v/>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="50">
         <f>ROUND(G11-G13,1)</f>
         <v/>
       </c>
@@ -3551,23 +4508,23 @@
           <t>Kontrolle: Endbestand ./. Kassenbestand lt. Bilanz (muss 0 sein)</t>
         </is>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="50">
         <f>ROUND(C11-'ESWE Bilanz'!C14,1)</f>
         <v/>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="50">
         <f>ROUND(D11-'ESWE Bilanz'!D14,1)</f>
         <v/>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="50">
         <f>ROUND(E11-'ESWE Bilanz'!E14,1)</f>
         <v/>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="50">
         <f>ROUND(F11-'ESWE Bilanz'!F14,1)</f>
         <v/>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="50">
         <f>ROUND(G11-'ESWE Bilanz'!G14,1)</f>
         <v/>
       </c>
@@ -3608,16 +4565,16 @@
   </cols>
   <sheetData>
     <row r="2" ht="21" customHeight="1">
-      <c r="B2" s="28" t="inlineStr">
+      <c r="B2" s="44" t="inlineStr">
         <is>
           <t>ESWE Versorgungs AG – Key Financials 2021–2025</t>
         </is>
       </c>
-      <c r="C2" s="28" t="n"/>
-      <c r="D2" s="28" t="n"/>
-      <c r="E2" s="28" t="n"/>
-      <c r="F2" s="28" t="n"/>
-      <c r="G2" s="28" t="n"/>
+      <c r="C2" s="44" t="n"/>
+      <c r="D2" s="44" t="n"/>
+      <c r="E2" s="44" t="n"/>
+      <c r="F2" s="44" t="n"/>
+      <c r="G2" s="44" t="n"/>
     </row>
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
@@ -3651,23 +4608,23 @@
           <t>Umsatzerlöse</t>
         </is>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="29">
         <f>'ESWE GuV'!C5</f>
         <v/>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="29">
         <f>'ESWE GuV'!D5</f>
         <v/>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="29">
         <f>'ESWE GuV'!E5</f>
         <v/>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="29">
         <f>'ESWE GuV'!F5</f>
         <v/>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="29">
         <f>'ESWE GuV'!G5</f>
         <v/>
       </c>
@@ -3678,23 +4635,23 @@
           <t>Gesamtleistung</t>
         </is>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="50">
         <f>'ESWE GuV'!C5+'ESWE GuV'!C6+'ESWE GuV'!C7</f>
         <v/>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="50">
         <f>'ESWE GuV'!D5+'ESWE GuV'!D6+'ESWE GuV'!D7</f>
         <v/>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="50">
         <f>'ESWE GuV'!E5+'ESWE GuV'!E6+'ESWE GuV'!E7</f>
         <v/>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="50">
         <f>'ESWE GuV'!F5+'ESWE GuV'!F6+'ESWE GuV'!F7</f>
         <v/>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="50">
         <f>'ESWE GuV'!G5+'ESWE GuV'!G6+'ESWE GuV'!G7</f>
         <v/>
       </c>
@@ -3705,50 +4662,50 @@
           <t>Rohertrag</t>
         </is>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="50">
         <f>C6-'ESWE GuV'!C9</f>
         <v/>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="50">
         <f>D6-'ESWE GuV'!D9</f>
         <v/>
       </c>
-      <c r="E7" s="34">
+      <c r="E7" s="50">
         <f>E6-'ESWE GuV'!E9</f>
         <v/>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="50">
         <f>F6-'ESWE GuV'!F9</f>
         <v/>
       </c>
-      <c r="G7" s="34">
+      <c r="G7" s="50">
         <f>G6-'ESWE GuV'!G9</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>(%) Rohertragsmarge</t>
         </is>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="51">
         <f>IFERROR(C7/C6,0)</f>
         <v/>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="51">
         <f>IFERROR(D7/D6,0)</f>
         <v/>
       </c>
-      <c r="E8" s="35">
+      <c r="E8" s="51">
         <f>IFERROR(E7/E6,0)</f>
         <v/>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="51">
         <f>IFERROR(F7/F6,0)</f>
         <v/>
       </c>
-      <c r="G8" s="35">
+      <c r="G8" s="51">
         <f>IFERROR(G7/G6,0)</f>
         <v/>
       </c>
@@ -3759,23 +4716,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="32">
         <f>C11+'ESWE GuV'!C11</f>
         <v/>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="32">
         <f>D11+'ESWE GuV'!D11</f>
         <v/>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="32">
         <f>E11+'ESWE GuV'!E11</f>
         <v/>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="32">
         <f>F11+'ESWE GuV'!F11</f>
         <v/>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="32">
         <f>G11+'ESWE GuV'!G11</f>
         <v/>
       </c>
@@ -3786,23 +4743,23 @@
           <t>EBIT / Betriebliches Ergebnis</t>
         </is>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="29">
         <f>'ESWE GuV'!C13</f>
         <v/>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="29">
         <f>'ESWE GuV'!D13</f>
         <v/>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="29">
         <f>'ESWE GuV'!E13</f>
         <v/>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="29">
         <f>'ESWE GuV'!F13</f>
         <v/>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="29">
         <f>'ESWE GuV'!G13</f>
         <v/>
       </c>
@@ -3813,23 +4770,23 @@
           <t>Beteiligungsergebnis</t>
         </is>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="24">
         <f>'ESWE GuV'!C15</f>
         <v/>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="24">
         <f>'ESWE GuV'!D15</f>
         <v/>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="24">
         <f>'ESWE GuV'!E15</f>
         <v/>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="24">
         <f>'ESWE GuV'!F15</f>
         <v/>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="24">
         <f>'ESWE GuV'!G15</f>
         <v/>
       </c>
@@ -3840,23 +4797,23 @@
           <t>Zinsergebnis</t>
         </is>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="24">
         <f>'ESWE GuV'!C17</f>
         <v/>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="24">
         <f>'ESWE GuV'!D17</f>
         <v/>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="24">
         <f>'ESWE GuV'!E17</f>
         <v/>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="24">
         <f>'ESWE GuV'!F17</f>
         <v/>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="24">
         <f>'ESWE GuV'!G17</f>
         <v/>
       </c>
@@ -3867,50 +4824,50 @@
           <t>Ergebnis vor Steuern</t>
         </is>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="29">
         <f>'ESWE GuV'!C18</f>
         <v/>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="29">
         <f>'ESWE GuV'!D18</f>
         <v/>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="29">
         <f>'ESWE GuV'!E18</f>
         <v/>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="29">
         <f>'ESWE GuV'!F18</f>
         <v/>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="29">
         <f>'ESWE GuV'!G18</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>Jahresüberschuss</t>
         </is>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="20">
         <f>'ESWE GuV'!C24</f>
         <v/>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="20">
         <f>'ESWE GuV'!D24</f>
         <v/>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="20">
         <f>'ESWE GuV'!E24</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="20">
         <f>'ESWE GuV'!F24</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="20">
         <f>'ESWE GuV'!G24</f>
         <v/>
       </c>
@@ -3921,23 +4878,23 @@
           <t>OCF – Operating Cash Flow</t>
         </is>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="24">
         <f>'ESWE Cashflow'!C5</f>
         <v/>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="24">
         <f>'ESWE Cashflow'!D5</f>
         <v/>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="24">
         <f>'ESWE Cashflow'!E5</f>
         <v/>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="24">
         <f>'ESWE Cashflow'!F5</f>
         <v/>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="24">
         <f>'ESWE Cashflow'!G5</f>
         <v/>
       </c>
@@ -3948,23 +4905,23 @@
           <t>ICF – Investing Cash Flow</t>
         </is>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="24">
         <f>'ESWE Cashflow'!C6</f>
         <v/>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="24">
         <f>'ESWE Cashflow'!D6</f>
         <v/>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="24">
         <f>'ESWE Cashflow'!E6</f>
         <v/>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="24">
         <f>'ESWE Cashflow'!F6</f>
         <v/>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="24">
         <f>'ESWE Cashflow'!G6</f>
         <v/>
       </c>
@@ -3975,50 +4932,50 @@
           <t>FCF – Financing Cash Flow</t>
         </is>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="24">
         <f>'ESWE Cashflow'!C7</f>
         <v/>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="24">
         <f>'ESWE Cashflow'!D7</f>
         <v/>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="24">
         <f>'ESWE Cashflow'!E7</f>
         <v/>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="24">
         <f>'ESWE Cashflow'!F7</f>
         <v/>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="24">
         <f>'ESWE Cashflow'!G7</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>FFCF – Free Cash Flow (OCF + ICF)</t>
         </is>
       </c>
-      <c r="C20" s="36">
+      <c r="C20" s="52">
         <f>C17+C18</f>
         <v/>
       </c>
-      <c r="D20" s="36">
+      <c r="D20" s="52">
         <f>D17+D18</f>
         <v/>
       </c>
-      <c r="E20" s="36">
+      <c r="E20" s="52">
         <f>E17+E18</f>
         <v/>
       </c>
-      <c r="F20" s="36">
+      <c r="F20" s="52">
         <f>F17+F18</f>
         <v/>
       </c>
-      <c r="G20" s="36">
+      <c r="G20" s="52">
         <f>G17+G18</f>
         <v/>
       </c>
@@ -4029,23 +4986,23 @@
           <t>Bilanzsumme</t>
         </is>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="24">
         <f>'ESWE Bilanz'!C17</f>
         <v/>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="24">
         <f>'ESWE Bilanz'!D17</f>
         <v/>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="24">
         <f>'ESWE Bilanz'!E17</f>
         <v/>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="24">
         <f>'ESWE Bilanz'!F17</f>
         <v/>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="24">
         <f>'ESWE Bilanz'!G17</f>
         <v/>
       </c>
@@ -4056,23 +5013,23 @@
           <t>Eigenkapital</t>
         </is>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="24">
         <f>'ESWE Bilanz'!C20</f>
         <v/>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="24">
         <f>'ESWE Bilanz'!D20</f>
         <v/>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="24">
         <f>'ESWE Bilanz'!E20</f>
         <v/>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="24">
         <f>'ESWE Bilanz'!F20</f>
         <v/>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="24">
         <f>'ESWE Bilanz'!G20</f>
         <v/>
       </c>
@@ -4083,23 +5040,23 @@
           <t>(%) Eigenkapitalquote</t>
         </is>
       </c>
-      <c r="C24" s="37">
+      <c r="C24" s="53">
         <f>IFERROR(C23/C22,0)</f>
         <v/>
       </c>
-      <c r="D24" s="37">
+      <c r="D24" s="53">
         <f>IFERROR(D23/D22,0)</f>
         <v/>
       </c>
-      <c r="E24" s="37">
+      <c r="E24" s="53">
         <f>IFERROR(E23/E22,0)</f>
         <v/>
       </c>
-      <c r="F24" s="37">
+      <c r="F24" s="53">
         <f>IFERROR(F23/F22,0)</f>
         <v/>
       </c>
-      <c r="G24" s="37">
+      <c r="G24" s="53">
         <f>IFERROR(G23/G22,0)</f>
         <v/>
       </c>
@@ -4110,50 +5067,50 @@
           <t>(%) Anlagenintensität</t>
         </is>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="41">
         <f>IFERROR('ESWE Bilanz'!C6/C22,0)</f>
         <v/>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="41">
         <f>IFERROR('ESWE Bilanz'!D6/D22,0)</f>
         <v/>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="41">
         <f>IFERROR('ESWE Bilanz'!E6/E22,0)</f>
         <v/>
       </c>
-      <c r="F25" s="27">
+      <c r="F25" s="41">
         <f>IFERROR('ESWE Bilanz'!F6/F22,0)</f>
         <v/>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="41">
         <f>IFERROR('ESWE Bilanz'!G6/G22,0)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>(%) Umsatzrendite</t>
         </is>
       </c>
-      <c r="C26" s="35">
+      <c r="C26" s="51">
         <f>IFERROR(C15/C5,0)</f>
         <v/>
       </c>
-      <c r="D26" s="35">
+      <c r="D26" s="51">
         <f>IFERROR(D15/D5,0)</f>
         <v/>
       </c>
-      <c r="E26" s="35">
+      <c r="E26" s="51">
         <f>IFERROR(E15/E5,0)</f>
         <v/>
       </c>
-      <c r="F26" s="35">
+      <c r="F26" s="51">
         <f>IFERROR(F15/F5,0)</f>
         <v/>
       </c>
-      <c r="G26" s="35">
+      <c r="G26" s="51">
         <f>IFERROR(G15/G5,0)</f>
         <v/>
       </c>
@@ -4164,23 +5121,23 @@
           <t>(-) Kassenbestand</t>
         </is>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="24">
         <f>'ESWE Bilanz'!C14</f>
         <v/>
       </c>
-      <c r="D27" s="17">
+      <c r="D27" s="24">
         <f>'ESWE Bilanz'!D14</f>
         <v/>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="24">
         <f>'ESWE Bilanz'!E14</f>
         <v/>
       </c>
-      <c r="F27" s="17">
+      <c r="F27" s="24">
         <f>'ESWE Bilanz'!F14</f>
         <v/>
       </c>
-      <c r="G27" s="17">
+      <c r="G27" s="24">
         <f>'ESWE Bilanz'!G14</f>
         <v/>
       </c>
@@ -4191,23 +5148,23 @@
           <t>(+) Verbindlichkeiten gegenüber Kreditinstituten</t>
         </is>
       </c>
-      <c r="C28" s="17">
+      <c r="C28" s="24">
         <f>'ESWE Bilanz'!C29</f>
         <v/>
       </c>
-      <c r="D28" s="17">
+      <c r="D28" s="24">
         <f>'ESWE Bilanz'!D29</f>
         <v/>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="24">
         <f>'ESWE Bilanz'!E29</f>
         <v/>
       </c>
-      <c r="F28" s="17">
+      <c r="F28" s="24">
         <f>'ESWE Bilanz'!F29</f>
         <v/>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="24">
         <f>'ESWE Bilanz'!G29</f>
         <v/>
       </c>
@@ -4218,50 +5175,50 @@
           <t>Net Debt</t>
         </is>
       </c>
-      <c r="C29" s="22">
+      <c r="C29" s="32">
         <f>C28-C27</f>
         <v/>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="32">
         <f>D28-D27</f>
         <v/>
       </c>
-      <c r="E29" s="22">
+      <c r="E29" s="32">
         <f>E28-E27</f>
         <v/>
       </c>
-      <c r="F29" s="22">
+      <c r="F29" s="32">
         <f>F28-F27</f>
         <v/>
       </c>
-      <c r="G29" s="22">
+      <c r="G29" s="32">
         <f>G28-G27</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>Net Debt / EBITDA</t>
         </is>
       </c>
-      <c r="C30" s="38">
+      <c r="C30" s="54">
         <f>IFERROR(C29/C10,0)</f>
         <v/>
       </c>
-      <c r="D30" s="38">
+      <c r="D30" s="54">
         <f>IFERROR(D29/D10,0)</f>
         <v/>
       </c>
-      <c r="E30" s="38">
+      <c r="E30" s="54">
         <f>IFERROR(E29/E10,0)</f>
         <v/>
       </c>
-      <c r="F30" s="38">
+      <c r="F30" s="54">
         <f>IFERROR(F29/F10,0)</f>
         <v/>
       </c>
-      <c r="G30" s="38">
+      <c r="G30" s="54">
         <f>IFERROR(G29/G10,0)</f>
         <v/>
       </c>
@@ -4272,50 +5229,50 @@
           <t>Capex (Gesamtinvestitionen inkl. Finanzanlagen)</t>
         </is>
       </c>
-      <c r="C32" s="19">
+      <c r="C32" s="29">
         <f>'ESWE Capex Revenue'!C14</f>
         <v/>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="29">
         <f>'ESWE Capex Revenue'!D14</f>
         <v/>
       </c>
-      <c r="E32" s="19">
+      <c r="E32" s="29">
         <f>'ESWE Capex Revenue'!E14</f>
         <v/>
       </c>
-      <c r="F32" s="19">
+      <c r="F32" s="29">
         <f>'ESWE Capex Revenue'!F14</f>
         <v/>
       </c>
-      <c r="G32" s="19">
+      <c r="G32" s="29">
         <f>'ESWE Capex Revenue'!G14</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="20" t="inlineStr">
+      <c r="B33" s="30" t="inlineStr">
         <is>
           <t>(%) Capex / Umsatzerlöse</t>
         </is>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="51">
         <f>IFERROR(C32/C5,0)</f>
         <v/>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="51">
         <f>IFERROR(D32/D5,0)</f>
         <v/>
       </c>
-      <c r="E33" s="35">
+      <c r="E33" s="51">
         <f>IFERROR(E32/E5,0)</f>
         <v/>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="51">
         <f>IFERROR(F32/F5,0)</f>
         <v/>
       </c>
-      <c r="G33" s="35">
+      <c r="G33" s="51">
         <f>IFERROR(G32/G5,0)</f>
         <v/>
       </c>
@@ -4348,23 +5305,23 @@
           <t>Strom (Mio. kWh)</t>
         </is>
       </c>
-      <c r="C36" s="39">
+      <c r="C36" s="55">
         <f>'ESWE Capex Revenue'!C18</f>
         <v/>
       </c>
-      <c r="D36" s="39">
+      <c r="D36" s="55">
         <f>'ESWE Capex Revenue'!D18</f>
         <v/>
       </c>
-      <c r="E36" s="39">
+      <c r="E36" s="55">
         <f>'ESWE Capex Revenue'!E18</f>
         <v/>
       </c>
-      <c r="F36" s="39">
+      <c r="F36" s="55">
         <f>'ESWE Capex Revenue'!F18</f>
         <v/>
       </c>
-      <c r="G36" s="39">
+      <c r="G36" s="55">
         <f>'ESWE Capex Revenue'!G18</f>
         <v/>
       </c>
@@ -4375,23 +5332,23 @@
           <t>Gas (Mio. kWh)</t>
         </is>
       </c>
-      <c r="C37" s="39">
+      <c r="C37" s="55">
         <f>'ESWE Capex Revenue'!C19</f>
         <v/>
       </c>
-      <c r="D37" s="39">
+      <c r="D37" s="55">
         <f>'ESWE Capex Revenue'!D19</f>
         <v/>
       </c>
-      <c r="E37" s="39">
+      <c r="E37" s="55">
         <f>'ESWE Capex Revenue'!E19</f>
         <v/>
       </c>
-      <c r="F37" s="39">
+      <c r="F37" s="55">
         <f>'ESWE Capex Revenue'!F19</f>
         <v/>
       </c>
-      <c r="G37" s="39">
+      <c r="G37" s="55">
         <f>'ESWE Capex Revenue'!G19</f>
         <v/>
       </c>
@@ -4402,23 +5359,23 @@
           <t>Wärme / Kälte (Mio. kWh)</t>
         </is>
       </c>
-      <c r="C38" s="39">
+      <c r="C38" s="55">
         <f>'ESWE Capex Revenue'!C20</f>
         <v/>
       </c>
-      <c r="D38" s="39">
+      <c r="D38" s="55">
         <f>'ESWE Capex Revenue'!D20</f>
         <v/>
       </c>
-      <c r="E38" s="39">
+      <c r="E38" s="55">
         <f>'ESWE Capex Revenue'!E20</f>
         <v/>
       </c>
-      <c r="F38" s="39">
+      <c r="F38" s="55">
         <f>'ESWE Capex Revenue'!F20</f>
         <v/>
       </c>
-      <c r="G38" s="39">
+      <c r="G38" s="55">
         <f>'ESWE Capex Revenue'!G20</f>
         <v/>
       </c>
@@ -4429,23 +5386,23 @@
           <t>Wassernetz (Mio. m³)</t>
         </is>
       </c>
-      <c r="C39" s="17">
+      <c r="C39" s="24">
         <f>'ESWE Capex Revenue'!C21</f>
         <v/>
       </c>
-      <c r="D39" s="17">
+      <c r="D39" s="24">
         <f>'ESWE Capex Revenue'!D21</f>
         <v/>
       </c>
-      <c r="E39" s="17">
+      <c r="E39" s="24">
         <f>'ESWE Capex Revenue'!E21</f>
         <v/>
       </c>
-      <c r="F39" s="17">
+      <c r="F39" s="24">
         <f>'ESWE Capex Revenue'!F21</f>
         <v/>
       </c>
-      <c r="G39" s="17">
+      <c r="G39" s="24">
         <f>'ESWE Capex Revenue'!G21</f>
         <v/>
       </c>
@@ -4486,16 +5443,16 @@
   </cols>
   <sheetData>
     <row r="2" ht="21" customHeight="1">
-      <c r="B2" s="28" t="inlineStr">
+      <c r="B2" s="44" t="inlineStr">
         <is>
           <t>ESWE Versorgungs AG – Investitionen, Umsatzerlöse und Absatz 2021–2025</t>
         </is>
       </c>
-      <c r="C2" s="28" t="n"/>
-      <c r="D2" s="28" t="n"/>
-      <c r="E2" s="28" t="n"/>
-      <c r="F2" s="28" t="n"/>
-      <c r="G2" s="28" t="n"/>
+      <c r="C2" s="44" t="n"/>
+      <c r="D2" s="44" t="n"/>
+      <c r="E2" s="44" t="n"/>
+      <c r="F2" s="44" t="n"/>
+      <c r="G2" s="44" t="n"/>
     </row>
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
@@ -4531,214 +5488,214 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="47" t="inlineStr">
         <is>
           <t>Stromversorgung</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n">
+      <c r="C6" s="48" t="n">
         <v>2.876</v>
       </c>
-      <c r="D6" s="32" t="n">
+      <c r="D6" s="48" t="n">
         <v>2.173</v>
       </c>
-      <c r="E6" s="32" t="n">
+      <c r="E6" s="48" t="n">
         <v>1.005</v>
       </c>
-      <c r="F6" s="32" t="n">
+      <c r="F6" s="48" t="n">
         <v>0.5679999999999999</v>
       </c>
-      <c r="G6" s="32" t="n">
+      <c r="G6" s="48" t="n">
         <v>0.982</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="47" t="inlineStr">
         <is>
           <t>Gasversorgung</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n">
+      <c r="C7" s="48" t="n">
         <v>9.439</v>
       </c>
-      <c r="D7" s="32" t="n">
+      <c r="D7" s="48" t="n">
         <v>4.249</v>
       </c>
-      <c r="E7" s="32" t="n">
+      <c r="E7" s="48" t="n">
         <v>2.139</v>
       </c>
-      <c r="F7" s="32" t="n">
+      <c r="F7" s="48" t="n">
         <v>2.393</v>
       </c>
-      <c r="G7" s="32" t="n">
+      <c r="G7" s="48" t="n">
         <v>2.991</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="47" t="inlineStr">
         <is>
           <t>Wasserversorgung</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n">
+      <c r="C8" s="48" t="n">
         <v>7.505</v>
       </c>
-      <c r="D8" s="32" t="n">
+      <c r="D8" s="48" t="n">
         <v>11.746</v>
       </c>
-      <c r="E8" s="32" t="n">
+      <c r="E8" s="48" t="n">
         <v>5.922</v>
       </c>
-      <c r="F8" s="32" t="n">
+      <c r="F8" s="48" t="n">
         <v>7.867</v>
       </c>
-      <c r="G8" s="32" t="n">
+      <c r="G8" s="48" t="n">
         <v>13.969</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" s="47" t="inlineStr">
         <is>
           <t>Wärmeversorgung</t>
         </is>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="48" t="n">
         <v>7.456</v>
       </c>
-      <c r="D9" s="32" t="n">
+      <c r="D9" s="48" t="n">
         <v>8.593</v>
       </c>
-      <c r="E9" s="32" t="n">
+      <c r="E9" s="48" t="n">
         <v>9.994999999999999</v>
       </c>
-      <c r="F9" s="32" t="n">
+      <c r="F9" s="48" t="n">
         <v>8.561</v>
       </c>
-      <c r="G9" s="32" t="n">
+      <c r="G9" s="48" t="n">
         <v>6.503</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="31" t="inlineStr">
+      <c r="B10" s="47" t="inlineStr">
         <is>
           <t>Telekommunikation</t>
         </is>
       </c>
-      <c r="C10" s="40" t="inlineStr">
+      <c r="C10" s="56" t="inlineStr">
         <is>
           <t>n.a.</t>
         </is>
       </c>
-      <c r="D10" s="40" t="inlineStr">
+      <c r="D10" s="56" t="inlineStr">
         <is>
           <t>n.a.</t>
         </is>
       </c>
-      <c r="E10" s="40" t="inlineStr">
+      <c r="E10" s="56" t="inlineStr">
         <is>
           <t>n.a.</t>
         </is>
       </c>
-      <c r="F10" s="32" t="n">
+      <c r="F10" s="48" t="n">
         <v>1.259</v>
       </c>
-      <c r="G10" s="40" t="inlineStr">
+      <c r="G10" s="56" t="inlineStr">
         <is>
           <t>n.a.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="31" t="inlineStr">
+      <c r="B11" s="47" t="inlineStr">
         <is>
           <t>Sonstige Bereiche</t>
         </is>
       </c>
-      <c r="C11" s="32" t="n">
+      <c r="C11" s="48" t="n">
         <v>1.748</v>
       </c>
-      <c r="D11" s="32" t="n">
+      <c r="D11" s="48" t="n">
         <v>1.059</v>
       </c>
-      <c r="E11" s="32" t="n">
+      <c r="E11" s="48" t="n">
         <v>0.8139999999999999</v>
       </c>
-      <c r="F11" s="32" t="n">
+      <c r="F11" s="48" t="n">
         <v>1.173</v>
       </c>
-      <c r="G11" s="32" t="n">
+      <c r="G11" s="48" t="n">
         <v>3.377</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="31" t="inlineStr">
+      <c r="B12" s="47" t="inlineStr">
         <is>
           <t>Gemeinsame Bereiche</t>
         </is>
       </c>
-      <c r="C12" s="40" t="inlineStr">
+      <c r="C12" s="56" t="inlineStr">
         <is>
           <t>n.a.</t>
         </is>
       </c>
-      <c r="D12" s="32" t="n">
+      <c r="D12" s="48" t="n">
         <v>1.851</v>
       </c>
-      <c r="E12" s="32" t="n">
+      <c r="E12" s="48" t="n">
         <v>5.599</v>
       </c>
-      <c r="F12" s="32" t="n">
+      <c r="F12" s="48" t="n">
         <v>3.426</v>
       </c>
-      <c r="G12" s="32" t="n">
+      <c r="G12" s="48" t="n">
         <v>3.957</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" s="47" t="inlineStr">
         <is>
           <t>Beteiligungen (Finanzanlagen)</t>
         </is>
       </c>
-      <c r="C13" s="32" t="n">
+      <c r="C13" s="48" t="n">
         <v>14.169</v>
       </c>
-      <c r="D13" s="32" t="n">
+      <c r="D13" s="48" t="n">
         <v>24.003</v>
       </c>
-      <c r="E13" s="32" t="n">
+      <c r="E13" s="48" t="n">
         <v>1.868</v>
       </c>
-      <c r="F13" s="32" t="n">
+      <c r="F13" s="48" t="n">
         <v>2.206</v>
       </c>
-      <c r="G13" s="32" t="n">
+      <c r="G13" s="48" t="n">
         <v>5.229</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Gesamtinvestitionen</t>
         </is>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="40">
         <f>SUM(C6:C13)</f>
         <v/>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="40">
         <f>SUM(D6:D13)</f>
         <v/>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="40">
         <f>SUM(E6:E13)</f>
         <v/>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="40">
         <f>SUM(F6:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="40">
         <f>SUM(G6:G13)</f>
         <v/>
       </c>
@@ -4751,90 +5708,90 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="31" t="inlineStr">
+      <c r="B18" s="47" t="inlineStr">
         <is>
           <t>Strom (Mio. kWh)</t>
         </is>
       </c>
-      <c r="C18" s="41" t="n">
+      <c r="C18" s="57" t="n">
         <v>946</v>
       </c>
-      <c r="D18" s="41" t="n">
+      <c r="D18" s="57" t="n">
         <v>877</v>
       </c>
-      <c r="E18" s="41" t="n">
+      <c r="E18" s="57" t="n">
         <v>731</v>
       </c>
-      <c r="F18" s="41" t="n">
+      <c r="F18" s="57" t="n">
         <v>609</v>
       </c>
-      <c r="G18" s="41" t="n">
+      <c r="G18" s="57" t="n">
         <v>605</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="31" t="inlineStr">
+      <c r="B19" s="47" t="inlineStr">
         <is>
           <t>Gas (Mio. kWh)</t>
         </is>
       </c>
-      <c r="C19" s="41" t="n">
+      <c r="C19" s="57" t="n">
         <v>2220</v>
       </c>
-      <c r="D19" s="41" t="n">
+      <c r="D19" s="57" t="n">
         <v>1811</v>
       </c>
-      <c r="E19" s="41" t="n">
+      <c r="E19" s="57" t="n">
         <v>1545</v>
       </c>
-      <c r="F19" s="41" t="n">
+      <c r="F19" s="57" t="n">
         <v>1461</v>
       </c>
-      <c r="G19" s="41" t="n">
+      <c r="G19" s="57" t="n">
         <v>1445</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="31" t="inlineStr">
+      <c r="B20" s="47" t="inlineStr">
         <is>
           <t>Wärme / Kälte (Mio. kWh)</t>
         </is>
       </c>
-      <c r="C20" s="41" t="n">
+      <c r="C20" s="57" t="n">
         <v>295</v>
       </c>
-      <c r="D20" s="41" t="n">
+      <c r="D20" s="57" t="n">
         <v>256</v>
       </c>
-      <c r="E20" s="41" t="n">
+      <c r="E20" s="57" t="n">
         <v>238</v>
       </c>
-      <c r="F20" s="41" t="n">
+      <c r="F20" s="57" t="n">
         <v>272</v>
       </c>
-      <c r="G20" s="41" t="n">
+      <c r="G20" s="57" t="n">
         <v>275</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="31" t="inlineStr">
+      <c r="B21" s="47" t="inlineStr">
         <is>
           <t>Wassernetz (Mio. m³)</t>
         </is>
       </c>
-      <c r="C21" s="32" t="n">
+      <c r="C21" s="48" t="n">
         <v>14.4</v>
       </c>
-      <c r="D21" s="32" t="n">
+      <c r="D21" s="48" t="n">
         <v>14.5</v>
       </c>
-      <c r="E21" s="32" t="n">
+      <c r="E21" s="48" t="n">
         <v>14.3</v>
       </c>
-      <c r="F21" s="32" t="n">
+      <c r="F21" s="48" t="n">
         <v>14.6</v>
       </c>
-      <c r="G21" s="32" t="n">
+      <c r="G21" s="48" t="n">
         <v>14.7</v>
       </c>
     </row>
@@ -4846,182 +5803,182 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="31" t="inlineStr">
+      <c r="B24" s="47" t="inlineStr">
         <is>
           <t>Stromversorgung (inkl. Handelsgeschäfte)</t>
         </is>
       </c>
-      <c r="C24" s="32" t="n">
+      <c r="C24" s="48" t="n">
         <v>215.722</v>
       </c>
-      <c r="D24" s="32" t="n">
+      <c r="D24" s="48" t="n">
         <v>207.826</v>
       </c>
-      <c r="E24" s="32" t="n">
+      <c r="E24" s="48" t="n">
         <v>268.87</v>
       </c>
-      <c r="F24" s="32" t="n">
+      <c r="F24" s="48" t="n">
         <v>200.133</v>
       </c>
-      <c r="G24" s="32" t="n">
+      <c r="G24" s="48" t="n">
         <v>190</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="31" t="inlineStr">
+      <c r="B25" s="47" t="inlineStr">
         <is>
           <t>Gasversorgung (inkl. Handelsgeschäfte)</t>
         </is>
       </c>
-      <c r="C25" s="32" t="n">
+      <c r="C25" s="48" t="n">
         <v>108.195</v>
       </c>
-      <c r="D25" s="32" t="n">
+      <c r="D25" s="48" t="n">
         <v>156.251</v>
       </c>
-      <c r="E25" s="32" t="n">
+      <c r="E25" s="48" t="n">
         <v>241.101</v>
       </c>
-      <c r="F25" s="32" t="n">
+      <c r="F25" s="48" t="n">
         <v>206.042</v>
       </c>
-      <c r="G25" s="32" t="n">
+      <c r="G25" s="48" t="n">
         <v>155.7</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="31" t="inlineStr">
+      <c r="B26" s="47" t="inlineStr">
         <is>
           <t>Wärmeversorgung</t>
         </is>
       </c>
-      <c r="C26" s="32" t="n">
+      <c r="C26" s="48" t="n">
         <v>30.495</v>
       </c>
-      <c r="D26" s="32" t="n">
+      <c r="D26" s="48" t="n">
         <v>35.26</v>
       </c>
-      <c r="E26" s="32" t="n">
+      <c r="E26" s="48" t="n">
         <v>40.545</v>
       </c>
-      <c r="F26" s="32" t="n">
+      <c r="F26" s="48" t="n">
         <v>45.961</v>
       </c>
-      <c r="G26" s="32" t="n">
+      <c r="G26" s="48" t="n">
         <v>43.7</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="31" t="inlineStr">
+      <c r="B27" s="47" t="inlineStr">
         <is>
           <t>Betriebsführung Wasserversorgung</t>
         </is>
       </c>
-      <c r="C27" s="32" t="n">
+      <c r="C27" s="48" t="n">
         <v>23.863</v>
       </c>
-      <c r="D27" s="32" t="n">
+      <c r="D27" s="48" t="n">
         <v>24.698</v>
       </c>
-      <c r="E27" s="32" t="n">
+      <c r="E27" s="48" t="n">
         <v>25.771</v>
       </c>
-      <c r="F27" s="32" t="n">
+      <c r="F27" s="48" t="n">
         <v>29.842</v>
       </c>
-      <c r="G27" s="32" t="n">
+      <c r="G27" s="48" t="n">
         <v>32.6</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="31" t="inlineStr">
+      <c r="B28" s="47" t="inlineStr">
         <is>
           <t>Wasserverkauf an WLW</t>
         </is>
       </c>
-      <c r="C28" s="32" t="n">
+      <c r="C28" s="48" t="n">
         <v>12.672</v>
       </c>
-      <c r="D28" s="32" t="n">
+      <c r="D28" s="48" t="n">
         <v>15.355</v>
       </c>
-      <c r="E28" s="32" t="n">
+      <c r="E28" s="48" t="n">
         <v>17.394</v>
       </c>
-      <c r="F28" s="32" t="n">
+      <c r="F28" s="48" t="n">
         <v>15.831</v>
       </c>
-      <c r="G28" s="32" t="n">
+      <c r="G28" s="48" t="n">
         <v>16.9</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="31" t="inlineStr">
+      <c r="B29" s="47" t="inlineStr">
         <is>
           <t>Konzerninterne Dienstleistungen</t>
         </is>
       </c>
-      <c r="C29" s="32" t="n">
+      <c r="C29" s="48" t="n">
         <v>22.855</v>
       </c>
-      <c r="D29" s="32" t="n">
+      <c r="D29" s="48" t="n">
         <v>21.16</v>
       </c>
-      <c r="E29" s="32" t="n">
+      <c r="E29" s="48" t="n">
         <v>22.017</v>
       </c>
-      <c r="F29" s="32" t="n">
+      <c r="F29" s="48" t="n">
         <v>21.457</v>
       </c>
-      <c r="G29" s="32" t="n">
+      <c r="G29" s="48" t="n">
         <v>20.2</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="31" t="inlineStr">
+      <c r="B30" s="47" t="inlineStr">
         <is>
           <t>Übrige Umsatzerlöse</t>
         </is>
       </c>
-      <c r="C30" s="32" t="n">
+      <c r="C30" s="48" t="n">
         <v>12.73</v>
       </c>
-      <c r="D30" s="32" t="n">
+      <c r="D30" s="48" t="n">
         <v>15.133</v>
       </c>
-      <c r="E30" s="32" t="n">
+      <c r="E30" s="48" t="n">
         <v>18.364</v>
       </c>
-      <c r="F30" s="32" t="n">
+      <c r="F30" s="48" t="n">
         <v>15.387</v>
       </c>
-      <c r="G30" s="32" t="n">
+      <c r="G30" s="48" t="n">
         <v>14.7</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="29" t="inlineStr">
+      <c r="B31" s="45" t="inlineStr">
         <is>
           <t>Umsätze lt. Aufteilung</t>
         </is>
       </c>
-      <c r="C31" s="30">
+      <c r="C31" s="46">
         <f>SUM(C24:C30)</f>
         <v/>
       </c>
-      <c r="D31" s="30">
+      <c r="D31" s="46">
         <f>SUM(D24:D30)</f>
         <v/>
       </c>
-      <c r="E31" s="30">
+      <c r="E31" s="46">
         <f>SUM(E24:E30)</f>
         <v/>
       </c>
-      <c r="F31" s="30">
+      <c r="F31" s="46">
         <f>SUM(F24:F30)</f>
         <v/>
       </c>
-      <c r="G31" s="30">
+      <c r="G31" s="46">
         <f>SUM(G24:G30)</f>
         <v/>
       </c>
@@ -5032,50 +5989,50 @@
           <t>nachrichtlich: Umsatzerlöse lt. GuV</t>
         </is>
       </c>
-      <c r="C32" s="17">
+      <c r="C32" s="24">
         <f>'ESWE GuV'!C5</f>
         <v/>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="24">
         <f>'ESWE GuV'!D5</f>
         <v/>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="24">
         <f>'ESWE GuV'!E5</f>
         <v/>
       </c>
-      <c r="F32" s="17">
+      <c r="F32" s="24">
         <f>'ESWE GuV'!F5</f>
         <v/>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="24">
         <f>'ESWE GuV'!G5</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="42" t="inlineStr">
+      <c r="B33" s="58" t="inlineStr">
         <is>
           <t>Kontrolle: Aufteilung ./. GuV (muss 0 sein; 2025 Rundung)</t>
         </is>
       </c>
-      <c r="C33" s="43">
+      <c r="C33" s="59">
         <f>ROUND(C31-C32,1)</f>
         <v/>
       </c>
-      <c r="D33" s="43">
+      <c r="D33" s="59">
         <f>ROUND(D31-D32,1)</f>
         <v/>
       </c>
-      <c r="E33" s="43">
+      <c r="E33" s="59">
         <f>ROUND(E31-E32,1)</f>
         <v/>
       </c>
-      <c r="F33" s="43">
+      <c r="F33" s="59">
         <f>ROUND(F31-F32,1)</f>
         <v/>
       </c>
-      <c r="G33" s="43">
+      <c r="G33" s="59">
         <f>ROUND(G31-G32,1)</f>
         <v/>
       </c>
@@ -5088,217 +6045,217 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="31" t="inlineStr">
+      <c r="B36" s="47" t="inlineStr">
         <is>
           <t>Stromversorgung (inkl. Handelsgeschäfte)</t>
         </is>
       </c>
-      <c r="C36" s="27">
+      <c r="C36" s="41">
         <f>IFERROR(C24/C$31,0)</f>
         <v/>
       </c>
-      <c r="D36" s="27">
+      <c r="D36" s="41">
         <f>IFERROR(D24/D$31,0)</f>
         <v/>
       </c>
-      <c r="E36" s="27">
+      <c r="E36" s="41">
         <f>IFERROR(E24/E$31,0)</f>
         <v/>
       </c>
-      <c r="F36" s="27">
+      <c r="F36" s="41">
         <f>IFERROR(F24/F$31,0)</f>
         <v/>
       </c>
-      <c r="G36" s="27">
+      <c r="G36" s="41">
         <f>IFERROR(G24/G$31,0)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="31" t="inlineStr">
+      <c r="B37" s="47" t="inlineStr">
         <is>
           <t>Gasversorgung (inkl. Handelsgeschäfte)</t>
         </is>
       </c>
-      <c r="C37" s="27">
+      <c r="C37" s="41">
         <f>IFERROR(C25/C$31,0)</f>
         <v/>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="41">
         <f>IFERROR(D25/D$31,0)</f>
         <v/>
       </c>
-      <c r="E37" s="27">
+      <c r="E37" s="41">
         <f>IFERROR(E25/E$31,0)</f>
         <v/>
       </c>
-      <c r="F37" s="27">
+      <c r="F37" s="41">
         <f>IFERROR(F25/F$31,0)</f>
         <v/>
       </c>
-      <c r="G37" s="27">
+      <c r="G37" s="41">
         <f>IFERROR(G25/G$31,0)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="31" t="inlineStr">
+      <c r="B38" s="47" t="inlineStr">
         <is>
           <t>Wärmeversorgung</t>
         </is>
       </c>
-      <c r="C38" s="27">
+      <c r="C38" s="41">
         <f>IFERROR(C26/C$31,0)</f>
         <v/>
       </c>
-      <c r="D38" s="27">
+      <c r="D38" s="41">
         <f>IFERROR(D26/D$31,0)</f>
         <v/>
       </c>
-      <c r="E38" s="27">
+      <c r="E38" s="41">
         <f>IFERROR(E26/E$31,0)</f>
         <v/>
       </c>
-      <c r="F38" s="27">
+      <c r="F38" s="41">
         <f>IFERROR(F26/F$31,0)</f>
         <v/>
       </c>
-      <c r="G38" s="27">
+      <c r="G38" s="41">
         <f>IFERROR(G26/G$31,0)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="31" t="inlineStr">
+      <c r="B39" s="47" t="inlineStr">
         <is>
           <t>Betriebsführung Wasserversorgung</t>
         </is>
       </c>
-      <c r="C39" s="27">
+      <c r="C39" s="41">
         <f>IFERROR(C27/C$31,0)</f>
         <v/>
       </c>
-      <c r="D39" s="27">
+      <c r="D39" s="41">
         <f>IFERROR(D27/D$31,0)</f>
         <v/>
       </c>
-      <c r="E39" s="27">
+      <c r="E39" s="41">
         <f>IFERROR(E27/E$31,0)</f>
         <v/>
       </c>
-      <c r="F39" s="27">
+      <c r="F39" s="41">
         <f>IFERROR(F27/F$31,0)</f>
         <v/>
       </c>
-      <c r="G39" s="27">
+      <c r="G39" s="41">
         <f>IFERROR(G27/G$31,0)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="31" t="inlineStr">
+      <c r="B40" s="47" t="inlineStr">
         <is>
           <t>Wasserverkauf an WLW</t>
         </is>
       </c>
-      <c r="C40" s="27">
+      <c r="C40" s="41">
         <f>IFERROR(C28/C$31,0)</f>
         <v/>
       </c>
-      <c r="D40" s="27">
+      <c r="D40" s="41">
         <f>IFERROR(D28/D$31,0)</f>
         <v/>
       </c>
-      <c r="E40" s="27">
+      <c r="E40" s="41">
         <f>IFERROR(E28/E$31,0)</f>
         <v/>
       </c>
-      <c r="F40" s="27">
+      <c r="F40" s="41">
         <f>IFERROR(F28/F$31,0)</f>
         <v/>
       </c>
-      <c r="G40" s="27">
+      <c r="G40" s="41">
         <f>IFERROR(G28/G$31,0)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="31" t="inlineStr">
+      <c r="B41" s="47" t="inlineStr">
         <is>
           <t>Konzerninterne Dienstleistungen</t>
         </is>
       </c>
-      <c r="C41" s="27">
+      <c r="C41" s="41">
         <f>IFERROR(C29/C$31,0)</f>
         <v/>
       </c>
-      <c r="D41" s="27">
+      <c r="D41" s="41">
         <f>IFERROR(D29/D$31,0)</f>
         <v/>
       </c>
-      <c r="E41" s="27">
+      <c r="E41" s="41">
         <f>IFERROR(E29/E$31,0)</f>
         <v/>
       </c>
-      <c r="F41" s="27">
+      <c r="F41" s="41">
         <f>IFERROR(F29/F$31,0)</f>
         <v/>
       </c>
-      <c r="G41" s="27">
+      <c r="G41" s="41">
         <f>IFERROR(G29/G$31,0)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="31" t="inlineStr">
+      <c r="B42" s="47" t="inlineStr">
         <is>
           <t>Übrige Umsatzerlöse</t>
         </is>
       </c>
-      <c r="C42" s="27">
+      <c r="C42" s="41">
         <f>IFERROR(C30/C$31,0)</f>
         <v/>
       </c>
-      <c r="D42" s="27">
+      <c r="D42" s="41">
         <f>IFERROR(D30/D$31,0)</f>
         <v/>
       </c>
-      <c r="E42" s="27">
+      <c r="E42" s="41">
         <f>IFERROR(E30/E$31,0)</f>
         <v/>
       </c>
-      <c r="F42" s="27">
+      <c r="F42" s="41">
         <f>IFERROR(F30/F$31,0)</f>
         <v/>
       </c>
-      <c r="G42" s="27">
+      <c r="G42" s="41">
         <f>IFERROR(G30/G$31,0)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="25" t="inlineStr">
+      <c r="B43" s="39" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="C43" s="44">
+      <c r="C43" s="60">
         <f>SUM(C36:C42)</f>
         <v/>
       </c>
-      <c r="D43" s="44">
+      <c r="D43" s="60">
         <f>SUM(D36:D42)</f>
         <v/>
       </c>
-      <c r="E43" s="44">
+      <c r="E43" s="60">
         <f>SUM(E36:E42)</f>
         <v/>
       </c>
-      <c r="F43" s="44">
+      <c r="F43" s="60">
         <f>SUM(F36:F42)</f>
         <v/>
       </c>
-      <c r="G43" s="44">
+      <c r="G43" s="60">
         <f>SUM(G36:G42)</f>
         <v/>
       </c>

--- a/ESWE_Versorgungs_AG_Financial_Model_2021_2025.xlsx
+++ b/ESWE_Versorgungs_AG_Financial_Model_2021_2025.xlsx
@@ -4191,23 +4191,23 @@
         </is>
       </c>
       <c r="C29" s="40">
-        <f>C24-SUM(C26:C28)</f>
+        <f>ROUND(C24-SUM(C26:C28),6)</f>
         <v/>
       </c>
       <c r="D29" s="40">
-        <f>D24-SUM(D26:D28)</f>
+        <f>ROUND(D24-SUM(D26:D28),6)</f>
         <v/>
       </c>
       <c r="E29" s="40">
-        <f>E24-SUM(E26:E28)</f>
+        <f>ROUND(E24-SUM(E26:E28),6)</f>
         <v/>
       </c>
       <c r="F29" s="40">
-        <f>F24-SUM(F26:F28)</f>
+        <f>ROUND(F24-SUM(F26:F28),6)</f>
         <v/>
       </c>
       <c r="G29" s="40">
-        <f>G24-SUM(G26:G28)</f>
+        <f>ROUND(G24-SUM(G26:G28),6)</f>
         <v/>
       </c>
     </row>
